--- a/AKC.xlsx
+++ b/AKC.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="126" documentId="11_E84A2F77117A4CCFEB3B98154B1BF678960CE3E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E741B45-41C4-4E3A-8790-C201F4BC409E}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="11_E84A2F77117A4CCFEB3B98154B1BF678960CE3E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8882F9E8-BF92-4E07-A079-7A3EF1EC9051}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1158,7 +1158,7 @@
     <t>https://youtube.com/shorts/9QIwX0NcdHo</t>
   </si>
   <si>
-    <t>Orientación</t>
+    <t>Orientacion</t>
   </si>
   <si>
     <t>Orientación aérea</t>
@@ -1841,7 +1841,7 @@
   <dimension ref="A1:K239"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.5703125" style="1" customWidth="1"/>

--- a/AKC.xlsx
+++ b/AKC.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="130" documentId="11_E84A2F77117A4CCFEB3B98154B1BF678960CE3E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8882F9E8-BF92-4E07-A079-7A3EF1EC9051}"/>
+  <xr:revisionPtr revIDLastSave="152" documentId="11_E84A2F77117A4CCFEB3B98154B1BF678960CE3E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C80184C5-0FEB-4996-8975-B5DFBD296C70}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6199,7 +6199,9 @@
         <v>375</v>
       </c>
       <c r="B188" s="2"/>
-      <c r="C188" s="2"/>
+      <c r="C188" s="2">
+        <v>1</v>
+      </c>
       <c r="D188" s="2" t="s">
         <v>376</v>
       </c>
@@ -6218,7 +6220,9 @@
         <v>375</v>
       </c>
       <c r="B189" s="2"/>
-      <c r="C189" s="2"/>
+      <c r="C189" s="2">
+        <v>1</v>
+      </c>
       <c r="D189" s="2" t="s">
         <v>376</v>
       </c>
@@ -6237,7 +6241,9 @@
         <v>375</v>
       </c>
       <c r="B190" s="2"/>
-      <c r="C190" s="2"/>
+      <c r="C190" s="2">
+        <v>1</v>
+      </c>
       <c r="D190" s="2" t="s">
         <v>376</v>
       </c>
@@ -6256,7 +6262,9 @@
         <v>375</v>
       </c>
       <c r="B191" s="2"/>
-      <c r="C191" s="2"/>
+      <c r="C191" s="2">
+        <v>1</v>
+      </c>
       <c r="D191" s="2" t="s">
         <v>376</v>
       </c>
@@ -6275,7 +6283,9 @@
         <v>375</v>
       </c>
       <c r="B192" s="2"/>
-      <c r="C192" s="2"/>
+      <c r="C192" s="2">
+        <v>1</v>
+      </c>
       <c r="D192" s="2" t="s">
         <v>376</v>
       </c>
@@ -6294,7 +6304,9 @@
         <v>375</v>
       </c>
       <c r="B193" s="2"/>
-      <c r="C193" s="2"/>
+      <c r="C193" s="2">
+        <v>1</v>
+      </c>
       <c r="D193" s="2" t="s">
         <v>376</v>
       </c>
@@ -6313,7 +6325,9 @@
         <v>375</v>
       </c>
       <c r="B194" s="2"/>
-      <c r="C194" s="2"/>
+      <c r="C194" s="2">
+        <v>1</v>
+      </c>
       <c r="D194" s="2" t="s">
         <v>376</v>
       </c>
@@ -6332,7 +6346,9 @@
         <v>375</v>
       </c>
       <c r="B195" s="2"/>
-      <c r="C195" s="2"/>
+      <c r="C195" s="2">
+        <v>1</v>
+      </c>
       <c r="D195" s="2" t="s">
         <v>376</v>
       </c>
@@ -6351,7 +6367,9 @@
         <v>375</v>
       </c>
       <c r="B196" s="2"/>
-      <c r="C196" s="2"/>
+      <c r="C196" s="2">
+        <v>1</v>
+      </c>
       <c r="D196" s="2" t="s">
         <v>376</v>
       </c>
@@ -6370,7 +6388,9 @@
         <v>375</v>
       </c>
       <c r="B197" s="2"/>
-      <c r="C197" s="2"/>
+      <c r="C197" s="2">
+        <v>1</v>
+      </c>
       <c r="D197" s="2" t="s">
         <v>376</v>
       </c>
@@ -6389,7 +6409,9 @@
         <v>375</v>
       </c>
       <c r="B198" s="2"/>
-      <c r="C198" s="2"/>
+      <c r="C198" s="2">
+        <v>1</v>
+      </c>
       <c r="D198" s="2" t="s">
         <v>376</v>
       </c>
@@ -6408,7 +6430,9 @@
         <v>375</v>
       </c>
       <c r="B199" s="2"/>
-      <c r="C199" s="2"/>
+      <c r="C199" s="2">
+        <v>1</v>
+      </c>
       <c r="D199" s="2" t="s">
         <v>376</v>
       </c>
@@ -6427,7 +6451,9 @@
         <v>375</v>
       </c>
       <c r="B200" s="2"/>
-      <c r="C200" s="2"/>
+      <c r="C200" s="2">
+        <v>1</v>
+      </c>
       <c r="D200" s="2" t="s">
         <v>376</v>
       </c>
@@ -6446,7 +6472,9 @@
         <v>375</v>
       </c>
       <c r="B201" s="2"/>
-      <c r="C201" s="2"/>
+      <c r="C201" s="2">
+        <v>1</v>
+      </c>
       <c r="D201" s="2" t="s">
         <v>376</v>
       </c>
@@ -6465,7 +6493,9 @@
         <v>375</v>
       </c>
       <c r="B202" s="2"/>
-      <c r="C202" s="2"/>
+      <c r="C202" s="2">
+        <v>1</v>
+      </c>
       <c r="D202" s="2" t="s">
         <v>376</v>
       </c>
@@ -6484,7 +6514,9 @@
         <v>375</v>
       </c>
       <c r="B203" s="2"/>
-      <c r="C203" s="2"/>
+      <c r="C203" s="2">
+        <v>1</v>
+      </c>
       <c r="D203" s="2" t="s">
         <v>376</v>
       </c>
@@ -6503,7 +6535,9 @@
         <v>375</v>
       </c>
       <c r="B204" s="2"/>
-      <c r="C204" s="2"/>
+      <c r="C204" s="2">
+        <v>1</v>
+      </c>
       <c r="D204" s="2" t="s">
         <v>376</v>
       </c>
@@ -6522,7 +6556,9 @@
         <v>375</v>
       </c>
       <c r="B205" s="2"/>
-      <c r="C205" s="2"/>
+      <c r="C205" s="2">
+        <v>1</v>
+      </c>
       <c r="D205" s="2" t="s">
         <v>376</v>
       </c>

--- a/AKC.xlsx
+++ b/AKC.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="152" documentId="11_E84A2F77117A4CCFEB3B98154B1BF678960CE3E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C80184C5-0FEB-4996-8975-B5DFBD296C70}"/>
+  <xr:revisionPtr revIDLastSave="156" documentId="11_E84A2F77117A4CCFEB3B98154B1BF678960CE3E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57F11C48-472A-4F29-A479-8CD368143536}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -411,15 +411,378 @@
     <t>https://youtube.com/shorts/_f5LLclJJrY</t>
   </si>
   <si>
+    <t>F ESP APA</t>
+  </si>
+  <si>
+    <t>Azarian a apoyo  Fuerza de anillos</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/kfJMvsCk3NA</t>
+  </si>
+  <si>
+    <t>Bajada cajones  Fuerza de anillos</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/WD7RYFpR2OY</t>
+  </si>
+  <si>
+    <t>Bajada de makuts bilateral Básicos de piso</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/crTI0esvU0Y</t>
+  </si>
+  <si>
+    <t>Preparación física</t>
+  </si>
+  <si>
+    <t>Balanceo cambio de toma saltada</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/k6ZptVovXkg</t>
+  </si>
+  <si>
+    <t>Balanceo en barras paralelas</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/PNCg2MCO8pw</t>
+  </si>
+  <si>
+    <t>Cambio full en barras paralelas</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/E9zsugUaHxc</t>
+  </si>
+  <si>
+    <t>Cambio interno en barras paralelas</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/1Rw5SFreGrE</t>
+  </si>
+  <si>
+    <t>Carrera con pateos extendidos al frente coordinación carrera</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/GH4m3zVmgSo</t>
+  </si>
+  <si>
+    <t>Carrera salto vertical por encima de caballo Potencia de entrada a botador</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/6lGBQJ-m9yM</t>
+  </si>
+  <si>
+    <t>Core barra elevación a rotación de cadera</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/ASo4z7Z53iw</t>
+  </si>
+  <si>
+    <t>Core y hombro cunita a manos</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/gWTwsQ3Cadk</t>
+  </si>
+  <si>
+    <t>Cristo apoyado  Fuerza de anillos</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/lIu_S_apGWE</t>
+  </si>
+  <si>
+    <t>De manos a plancha Dorsal  Fuerza de anillos</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/MRc1ArTyKRY</t>
+  </si>
+  <si>
+    <t>Desplazamiento lateral</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/pLOMmVJqbv0</t>
+  </si>
+  <si>
+    <t>Doble adelante de caja Plantados</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/CcqznLBZfbQ</t>
+  </si>
+  <si>
+    <t>Doble atrás de cajón Plantados</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/cOz9AN5hguE</t>
+  </si>
+  <si>
+    <t>Doble giro atrás de talacha en piso Básicos de piso</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/iA_8lc6oqMg</t>
+  </si>
+  <si>
+    <t>Elevación frontal abdomen core barra</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/nDCsUz91KX8</t>
+  </si>
+  <si>
+    <t>En parado de manos 5 pasos avance, giro, 5 pasos, giro Básicos de piso</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/x_1uTKFw_QI</t>
+  </si>
+  <si>
+    <t>Endo cerrado a manos en pared con paralelas piso Brazos extendidos</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/K8CyqzQuA8c</t>
+  </si>
+  <si>
+    <t>Fuerza de maltese rango amplio e isometrico</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/C9R2HLB311Q</t>
+  </si>
+  <si>
+    <t>Fuerza especifica para gigantes y felgues de paralelas</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/nL_EdrEPy7M</t>
+  </si>
+  <si>
+    <t>Fuerza y flex especifica de Adlers, italianos y checos</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/UuZqxJITyHE</t>
+  </si>
+  <si>
+    <t>Ganchos invertidos</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/xr5KsOx-kfs</t>
+  </si>
+  <si>
+    <t>Gigantes en barras paralelas</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/TysfvPmc7EU</t>
+  </si>
+  <si>
+    <t>Impulso a manos sostenido paralelas</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/1RUd60pybfA</t>
+  </si>
+  <si>
+    <t>Impulso atrás de braquial a parado de manos</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/CIL4D5t5u4s</t>
+  </si>
+  <si>
+    <t>Impulso plancha en arzones Preparación física paralelas Brazos flexionados</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/Rs_ZsTMBYOE</t>
+  </si>
+  <si>
+    <t>Kato a manos en anillos Brazos extendidos  Fuerza anillos</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/QIxxsKxALvs</t>
+  </si>
+  <si>
+    <t>Lagartija con pelota para plancha en anillos</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/NmqLvtuvYZU</t>
+  </si>
+  <si>
+    <t>Lagartija inversa en anillos Brazos flexionados</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/Bgz4ysSes4U</t>
+  </si>
+  <si>
+    <t>Línea de Adlers Básicos de piso</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/mGWThakBb7w</t>
+  </si>
+  <si>
+    <t>Líneas de parados de manos</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/fdAHOOs4F-0</t>
+  </si>
+  <si>
+    <t>Lsit a parado manos cerrada en arzon Brazos extendidos Control de parado de manos</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/tBwd7bh1GfE</t>
+  </si>
+  <si>
+    <t>Maltese a 45 Fuerza de anillos</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/z6bzZIPHAAI</t>
+  </si>
+  <si>
+    <t>Maltese con liga desde apoyo</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/ULXDWtKU1gY</t>
+  </si>
+  <si>
+    <t>Marcha coordinada coordinación carrera</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/caKviSCJb4E</t>
+  </si>
+  <si>
+    <t>Marcha lenta coordinada coordinación carrera</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/NVCoPUqV9gg</t>
+  </si>
+  <si>
+    <t>Marcha saltada coordinada coordinación carrera</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/svbQQQbKS0Y</t>
+  </si>
+  <si>
+    <t>Minicristo  Fuerza de anillos</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/kE-PKCCcA2I</t>
+  </si>
+  <si>
+    <t>Mortal agrupado, carpado adelante en piso Rebotes en piso</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/VQyEMJ3eSow</t>
+  </si>
+  <si>
+    <t>Mortal Agrupado, extendido adelante Rebotes en piso</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/YMsrFmx1nQY</t>
+  </si>
+  <si>
+    <t>Pateos extendidos al frente coordinación carrera</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/GtPzLsgMmls</t>
+  </si>
+  <si>
+    <t>Pateos extendidos atrás coordinación carrera</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/YBFSVIXIqTg</t>
+  </si>
+  <si>
+    <t>Pechadas a cambio en barras paralelas</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/btkUlUIXGBY</t>
+  </si>
+  <si>
+    <t>Plancha a maltese  Fuerza de anillos</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/9n9mfE7wxoo</t>
+  </si>
+  <si>
+    <t>Plancha facial, plancha Dorsal en anillos</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/w81GELw0xMs</t>
+  </si>
+  <si>
+    <t>Push braquial  Brazos flexionados  Preparación física paralelas</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/c31OKR2uMEw</t>
+  </si>
+  <si>
+    <t>Resorte a una, resorte a dos en piso Rebotes en piso</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/m239wtFI498</t>
+  </si>
+  <si>
+    <t>Resorte, león, mortal carpado en piso Rebotes en piso</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/HPW7Q01-2LQ</t>
+  </si>
+  <si>
+    <t>Rodada atrás a manos regreso a sisonne Básicos de piso</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/QXb5eGB2hqo</t>
+  </si>
+  <si>
+    <t>Rodada atrás a manos, giros y rebotes Básicos de piso</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/JPOpOdjCm_Q</t>
+  </si>
+  <si>
+    <t>Rodada L a manos giro, rebote Básicos de piso</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/OzCjBIcPDZI</t>
+  </si>
+  <si>
+    <t>Rotacion elevacion en braquial core barra</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/GJ6TD_GCP98</t>
+  </si>
+  <si>
+    <t>Rotaciones extendidas core barra y brazos flexionados</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/8D3qqB5I8YM</t>
+  </si>
+  <si>
+    <t>Salida de Lsit a 1/2 kato</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/p-7Gh6dWWk8</t>
+  </si>
+  <si>
+    <t>Salto potente</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/WMIMl0VbUrQ</t>
+  </si>
+  <si>
+    <t>Sprint progresivo</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/kV6iApwHZQU</t>
+  </si>
+  <si>
+    <t>Sprints</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/8Lq3YOO6oeg</t>
+  </si>
+  <si>
+    <t>Yogui coordinación carrera</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/9QIwX0NcdHo</t>
+  </si>
+  <si>
     <t>Fuerza</t>
   </si>
   <si>
     <t>Lunes</t>
   </si>
   <si>
-    <t>Preparación física</t>
-  </si>
-  <si>
     <t>Curl para bíceps y triceps</t>
   </si>
   <si>
@@ -795,370 +1158,7 @@
     <t>https://youtube.com/shorts/I9CPmi6pxyQ</t>
   </si>
   <si>
-    <t>F ESP APA</t>
-  </si>
-  <si>
-    <t>Azarian a apoyo  Fuerza de anillos</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/kfJMvsCk3NA</t>
-  </si>
-  <si>
-    <t>Bajada cajones  Fuerza de anillos</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/WD7RYFpR2OY</t>
-  </si>
-  <si>
-    <t>Bajada de makuts bilateral Básicos de piso</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/crTI0esvU0Y</t>
-  </si>
-  <si>
-    <t>Balanceo cambio de toma saltada</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/k6ZptVovXkg</t>
-  </si>
-  <si>
-    <t>Balanceo en barras paralelas</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/PNCg2MCO8pw</t>
-  </si>
-  <si>
-    <t>Cambio full en barras paralelas</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/E9zsugUaHxc</t>
-  </si>
-  <si>
-    <t>Cambio interno en barras paralelas</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/1Rw5SFreGrE</t>
-  </si>
-  <si>
-    <t>Carrera con pateos extendidos al frente coordinación carrera</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/GH4m3zVmgSo</t>
-  </si>
-  <si>
-    <t>Carrera salto vertical por encima de caballo Potencia de entrada a botador</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/6lGBQJ-m9yM</t>
-  </si>
-  <si>
-    <t>Core barra elevación a rotación de cadera</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/ASo4z7Z53iw</t>
-  </si>
-  <si>
-    <t>Core y hombro cunita a manos</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/gWTwsQ3Cadk</t>
-  </si>
-  <si>
-    <t>Cristo apoyado  Fuerza de anillos</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/lIu_S_apGWE</t>
-  </si>
-  <si>
-    <t>De manos a plancha Dorsal  Fuerza de anillos</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/MRc1ArTyKRY</t>
-  </si>
-  <si>
-    <t>Desplazamiento lateral</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/pLOMmVJqbv0</t>
-  </si>
-  <si>
-    <t>Doble adelante de caja Plantados</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/CcqznLBZfbQ</t>
-  </si>
-  <si>
-    <t>Doble atrás de cajón Plantados</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/cOz9AN5hguE</t>
-  </si>
-  <si>
-    <t>Doble giro atrás de talacha en piso Básicos de piso</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/iA_8lc6oqMg</t>
-  </si>
-  <si>
-    <t>Elevación frontal abdomen core barra</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/nDCsUz91KX8</t>
-  </si>
-  <si>
-    <t>En parado de manos 5 pasos avance, giro, 5 pasos, giro Básicos de piso</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/x_1uTKFw_QI</t>
-  </si>
-  <si>
-    <t>Endo cerrado a manos en pared con paralelas piso Brazos extendidos</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/K8CyqzQuA8c</t>
-  </si>
-  <si>
-    <t>Fuerza de maltese rango amplio e isometrico</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/C9R2HLB311Q</t>
-  </si>
-  <si>
-    <t>Fuerza especifica para gigantes y felgues de paralelas</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/nL_EdrEPy7M</t>
-  </si>
-  <si>
-    <t>Fuerza y flex especifica de Adlers, italianos y checos</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/UuZqxJITyHE</t>
-  </si>
-  <si>
-    <t>Ganchos invertidos</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/xr5KsOx-kfs</t>
-  </si>
-  <si>
-    <t>Gigantes en barras paralelas</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/TysfvPmc7EU</t>
-  </si>
-  <si>
-    <t>Impulso a manos sostenido paralelas</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/1RUd60pybfA</t>
-  </si>
-  <si>
-    <t>Impulso atrás de braquial a parado de manos</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/CIL4D5t5u4s</t>
-  </si>
-  <si>
-    <t>Impulso plancha en arzones Preparación física paralelas Brazos flexionados</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/Rs_ZsTMBYOE</t>
-  </si>
-  <si>
-    <t>Kato a manos en anillos Brazos extendidos  Fuerza anillos</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/QIxxsKxALvs</t>
-  </si>
-  <si>
-    <t>Lagartija con pelota para plancha en anillos</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/NmqLvtuvYZU</t>
-  </si>
-  <si>
-    <t>Lagartija inversa en anillos Brazos flexionados</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/Bgz4ysSes4U</t>
-  </si>
-  <si>
-    <t>Línea de Adlers Básicos de piso</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/mGWThakBb7w</t>
-  </si>
-  <si>
-    <t>Líneas de parados de manos</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/fdAHOOs4F-0</t>
-  </si>
-  <si>
-    <t>Lsit a parado manos cerrada en arzon Brazos extendidos Control de parado de manos</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/tBwd7bh1GfE</t>
-  </si>
-  <si>
-    <t>Maltese a 45 Fuerza de anillos</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/z6bzZIPHAAI</t>
-  </si>
-  <si>
-    <t>Maltese con liga desde apoyo</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/ULXDWtKU1gY</t>
-  </si>
-  <si>
-    <t>Marcha coordinada coordinación carrera</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/caKviSCJb4E</t>
-  </si>
-  <si>
-    <t>Marcha lenta coordinada coordinación carrera</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/NVCoPUqV9gg</t>
-  </si>
-  <si>
-    <t>Marcha saltada coordinada coordinación carrera</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/svbQQQbKS0Y</t>
-  </si>
-  <si>
-    <t>Minicristo  Fuerza de anillos</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/kE-PKCCcA2I</t>
-  </si>
-  <si>
-    <t>Mortal agrupado, carpado adelante en piso Rebotes en piso</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/VQyEMJ3eSow</t>
-  </si>
-  <si>
-    <t>Mortal Agrupado, extendido adelante Rebotes en piso</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/YMsrFmx1nQY</t>
-  </si>
-  <si>
-    <t>Pateos extendidos al frente coordinación carrera</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/GtPzLsgMmls</t>
-  </si>
-  <si>
-    <t>Pateos extendidos atrás coordinación carrera</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/YBFSVIXIqTg</t>
-  </si>
-  <si>
-    <t>Pechadas a cambio en barras paralelas</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/btkUlUIXGBY</t>
-  </si>
-  <si>
-    <t>Plancha a maltese  Fuerza de anillos</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/9n9mfE7wxoo</t>
-  </si>
-  <si>
-    <t>Plancha facial, plancha Dorsal en anillos</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/w81GELw0xMs</t>
-  </si>
-  <si>
-    <t>Push braquial  Brazos flexionados  Preparación física paralelas</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/c31OKR2uMEw</t>
-  </si>
-  <si>
-    <t>Resorte a una, resorte a dos en piso Rebotes en piso</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/m239wtFI498</t>
-  </si>
-  <si>
-    <t>Resorte, león, mortal carpado en piso Rebotes en piso</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/HPW7Q01-2LQ</t>
-  </si>
-  <si>
-    <t>Rodada atrás a manos regreso a sisonne Básicos de piso</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/QXb5eGB2hqo</t>
-  </si>
-  <si>
-    <t>Rodada atrás a manos, giros y rebotes Básicos de piso</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/JPOpOdjCm_Q</t>
-  </si>
-  <si>
-    <t>Rodada L a manos giro, rebote Básicos de piso</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/OzCjBIcPDZI</t>
-  </si>
-  <si>
-    <t>Rotacion elevacion en braquial core barra</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/GJ6TD_GCP98</t>
-  </si>
-  <si>
-    <t>Rotaciones extendidas core barra y brazos flexionados</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/8D3qqB5I8YM</t>
-  </si>
-  <si>
-    <t>Salida de Lsit a 1/2 kato</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/p-7Gh6dWWk8</t>
-  </si>
-  <si>
-    <t>Salto potente</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/WMIMl0VbUrQ</t>
-  </si>
-  <si>
-    <t>Sprint progresivo</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/kV6iApwHZQU</t>
-  </si>
-  <si>
-    <t>Sprints</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/8Lq3YOO6oeg</t>
-  </si>
-  <si>
-    <t>Yogui coordinación carrera</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/9QIwX0NcdHo</t>
-  </si>
-  <si>
-    <t>Orientacion</t>
+    <t>Orientación</t>
   </si>
   <si>
     <t>Orientación aérea</t>
@@ -2931,2702 +2931,2582 @@
       <c r="A57" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C57" s="2">
-        <v>1</v>
-      </c>
-      <c r="D57" s="2" t="s">
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F57" s="2">
-        <v>2</v>
-      </c>
-      <c r="G57" s="2">
-        <v>10</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C58" s="2">
-        <v>1</v>
-      </c>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
-        <v>128</v>
+        <v>13</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F58" s="2">
-        <v>2</v>
-      </c>
-      <c r="G58" s="2">
-        <v>10</v>
-      </c>
-      <c r="H58" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C59" s="2">
-        <v>1</v>
-      </c>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
       <c r="D59" s="2" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F59" s="2">
-        <v>2</v>
-      </c>
-      <c r="G59" s="2">
-        <v>10</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
       <c r="I59" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C60" s="2">
-        <v>1</v>
-      </c>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
       <c r="D60" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="F60" s="2">
-        <v>2</v>
-      </c>
-      <c r="G60" s="2">
-        <v>10</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
       <c r="I60" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C61" s="2">
-        <v>1</v>
-      </c>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
       <c r="D61" s="2" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F61" s="2">
-        <v>2</v>
-      </c>
-      <c r="G61" s="2">
-        <v>10</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
       <c r="I61" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C62" s="2">
-        <v>1</v>
-      </c>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
       <c r="D62" s="2" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F62" s="2">
-        <v>2</v>
-      </c>
-      <c r="G62" s="2">
-        <v>10</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
       <c r="I62" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C63" s="2">
-        <v>1</v>
-      </c>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
       <c r="D63" s="2" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="F63" s="2">
-        <v>2</v>
-      </c>
-      <c r="G63" s="2">
-        <v>10</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
       <c r="I63" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C64" s="2">
-        <v>1</v>
-      </c>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
       <c r="D64" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F64" s="2">
-        <v>2</v>
-      </c>
-      <c r="G64" s="2">
-        <v>10</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
       <c r="I64" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C65" s="2">
-        <v>1</v>
-      </c>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
       <c r="D65" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F65" s="2">
-        <v>2</v>
-      </c>
-      <c r="G65" s="2">
-        <v>10</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
       <c r="I65" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C66" s="2">
-        <v>1</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="F66" s="2">
-        <v>2</v>
-      </c>
-      <c r="G66" s="2">
-        <v>10</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>130</v>
-      </c>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
       <c r="I66" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C67" s="2">
-        <v>1</v>
-      </c>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
       <c r="D67" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F67" s="2">
-        <v>2</v>
-      </c>
-      <c r="G67" s="2">
-        <v>10</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
       <c r="I67" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C68" s="2">
-        <v>1</v>
-      </c>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
       <c r="D68" s="2" t="s">
-        <v>128</v>
+        <v>13</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F68" s="2">
-        <v>2</v>
-      </c>
-      <c r="G68" s="2">
-        <v>10</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
       <c r="I68" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C69" s="2">
-        <v>1</v>
-      </c>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
       <c r="D69" s="2" t="s">
-        <v>128</v>
+        <v>13</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F69" s="2">
-        <v>2</v>
-      </c>
-      <c r="G69" s="2">
-        <v>10</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
       <c r="I69" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C70" s="2">
-        <v>1</v>
-      </c>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
       <c r="D70" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="F70" s="2">
-        <v>2</v>
-      </c>
-      <c r="G70" s="2">
-        <v>10</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
       <c r="I70" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C71" s="2">
-        <v>1</v>
-      </c>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
       <c r="D71" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F71" s="2">
-        <v>2</v>
-      </c>
-      <c r="G71" s="2">
-        <v>10</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
       <c r="I71" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C72" s="2">
-        <v>1</v>
-      </c>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
       <c r="D72" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="F72" s="2">
-        <v>2</v>
-      </c>
-      <c r="G72" s="2">
-        <v>10</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
       <c r="I72" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C73" s="2">
-        <v>1</v>
-      </c>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
       <c r="D73" s="2" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F73" s="2">
-        <v>2</v>
-      </c>
-      <c r="G73" s="2">
-        <v>10</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
       <c r="I73" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="C74" s="2">
-        <v>1</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="F74" s="2">
-        <v>2</v>
-      </c>
-      <c r="G74" s="2">
-        <v>10</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C75" s="2">
-        <v>1</v>
-      </c>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
       <c r="D75" s="2" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F75" s="2">
-        <v>2</v>
-      </c>
-      <c r="G75" s="2">
-        <v>10</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
       <c r="I75" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C76" s="2">
-        <v>1</v>
-      </c>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
       <c r="D76" s="2" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F76" s="2">
-        <v>2</v>
-      </c>
-      <c r="G76" s="2">
-        <v>10</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
       <c r="I76" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C77" s="2">
-        <v>1</v>
-      </c>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
       <c r="D77" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="F77" s="2">
-        <v>2</v>
-      </c>
-      <c r="G77" s="2">
-        <v>10</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
       <c r="I77" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C78" s="2">
-        <v>1</v>
-      </c>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
       <c r="D78" s="2" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F78" s="2">
-        <v>2</v>
-      </c>
-      <c r="G78" s="2">
-        <v>10</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
       <c r="I78" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C79" s="2">
-        <v>1</v>
-      </c>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
       <c r="D79" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="F79" s="2">
-        <v>2</v>
-      </c>
-      <c r="G79" s="2">
-        <v>10</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
       <c r="I79" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C80" s="2">
-        <v>1</v>
-      </c>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
       <c r="D80" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="F80" s="2">
-        <v>2</v>
-      </c>
-      <c r="G80" s="2">
-        <v>10</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
       <c r="I80" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C81" s="2">
-        <v>2</v>
-      </c>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
       <c r="D81" s="2" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F81" s="2">
-        <v>2</v>
-      </c>
-      <c r="G81" s="2">
-        <v>8</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
       <c r="I81" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C82" s="2">
-        <v>2</v>
-      </c>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
       <c r="D82" s="2" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="F82" s="2">
-        <v>2</v>
-      </c>
-      <c r="G82" s="2">
-        <v>8</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
       <c r="I82" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C83" s="2">
-        <v>2</v>
-      </c>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
       <c r="D83" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="F83" s="2">
-        <v>2</v>
-      </c>
-      <c r="G83" s="2">
-        <v>8</v>
-      </c>
-      <c r="H83" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C84" s="2">
-        <v>2</v>
-      </c>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
       <c r="D84" s="2" t="s">
-        <v>128</v>
+        <v>29</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="F84" s="2">
-        <v>2</v>
-      </c>
-      <c r="G84" s="2">
-        <v>8</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
       <c r="I84" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C85" s="2">
-        <v>2</v>
-      </c>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
       <c r="D85" s="2" t="s">
-        <v>128</v>
+        <v>13</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F85" s="2">
-        <v>2</v>
-      </c>
-      <c r="G85" s="2">
-        <v>8</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
       <c r="I85" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C86" s="2">
-        <v>2</v>
-      </c>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
       <c r="D86" s="2" t="s">
-        <v>128</v>
+        <v>13</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F86" s="2">
-        <v>2</v>
-      </c>
-      <c r="G86" s="2">
-        <v>8</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
       <c r="I86" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C87" s="2">
-        <v>2</v>
-      </c>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
       <c r="D87" s="2" t="s">
-        <v>128</v>
+        <v>13</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="F87" s="2">
-        <v>2</v>
-      </c>
-      <c r="G87" s="2">
-        <v>8</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
       <c r="I87" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C88" s="2">
-        <v>2</v>
-      </c>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
       <c r="D88" s="2" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F88" s="2">
-        <v>2</v>
-      </c>
-      <c r="G88" s="2">
-        <v>8</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
       <c r="I88" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C89" s="2">
-        <v>2</v>
-      </c>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
       <c r="D89" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F89" s="2">
-        <v>2</v>
-      </c>
-      <c r="G89" s="2">
-        <v>8</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
       <c r="I89" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C90" s="2">
-        <v>2</v>
-      </c>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
       <c r="D90" s="2" t="s">
-        <v>128</v>
+        <v>29</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="F90" s="2">
-        <v>2</v>
-      </c>
-      <c r="G90" s="2">
-        <v>8</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
       <c r="I90" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C91" s="2">
-        <v>2</v>
-      </c>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
       <c r="D91" s="2" t="s">
-        <v>128</v>
+        <v>13</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="F91" s="2">
-        <v>2</v>
-      </c>
-      <c r="G91" s="2">
-        <v>8</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
       <c r="I91" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C92" s="2">
-        <v>2</v>
-      </c>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
       <c r="D92" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F92" s="2">
-        <v>2</v>
-      </c>
-      <c r="G92" s="2">
-        <v>8</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
       <c r="I92" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C93" s="2">
-        <v>2</v>
-      </c>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
       <c r="D93" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="F93" s="2">
-        <v>2</v>
-      </c>
-      <c r="G93" s="2">
-        <v>8</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
       <c r="I93" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C94" s="2">
-        <v>2</v>
-      </c>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
       <c r="D94" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F94" s="2">
-        <v>2</v>
-      </c>
-      <c r="G94" s="2">
-        <v>8</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
       <c r="I94" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C95" s="2">
-        <v>2</v>
-      </c>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
       <c r="D95" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F95" s="2">
-        <v>2</v>
-      </c>
-      <c r="G95" s="2">
-        <v>8</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
       <c r="I95" s="3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C96" s="2">
-        <v>2</v>
-      </c>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
       <c r="D96" s="2" t="s">
-        <v>128</v>
+        <v>13</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F96" s="2">
-        <v>2</v>
-      </c>
-      <c r="G96" s="2">
-        <v>8</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
       <c r="I96" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C97" s="2">
-        <v>2</v>
-      </c>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
       <c r="D97" s="2" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="F97" s="2">
-        <v>2</v>
-      </c>
-      <c r="G97" s="2">
-        <v>8</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
       <c r="I97" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C98" s="2">
-        <v>2</v>
-      </c>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
       <c r="D98" s="2" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F98" s="2">
-        <v>2</v>
-      </c>
-      <c r="G98" s="2">
-        <v>8</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
       <c r="I98" s="3" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C99" s="2">
-        <v>2</v>
-      </c>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
       <c r="D99" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="F99" s="2">
-        <v>2</v>
-      </c>
-      <c r="G99" s="2">
-        <v>8</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
       <c r="I99" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C100" s="2">
-        <v>2</v>
-      </c>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
       <c r="D100" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F100" s="2">
-        <v>2</v>
-      </c>
-      <c r="G100" s="2">
-        <v>8</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
       <c r="I100" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C101" s="2">
-        <v>2</v>
-      </c>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
       <c r="D101" s="2" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F101" s="2">
-        <v>2</v>
-      </c>
-      <c r="G101" s="2">
-        <v>8</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
       <c r="I101" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C102" s="2">
-        <v>2</v>
-      </c>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
       <c r="D102" s="2" t="s">
-        <v>128</v>
+        <v>13</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F102" s="2">
-        <v>2</v>
-      </c>
-      <c r="G102" s="2">
-        <v>8</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
       <c r="I102" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C103" s="2">
-        <v>2</v>
-      </c>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
       <c r="D103" s="2" t="s">
-        <v>128</v>
+        <v>13</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="F103" s="2">
-        <v>2</v>
-      </c>
-      <c r="G103" s="2">
-        <v>8</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
       <c r="I103" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C104" s="2">
-        <v>3</v>
-      </c>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
       <c r="D104" s="2" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="F104" s="2">
-        <v>2</v>
-      </c>
-      <c r="G104" s="2">
-        <v>8</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
       <c r="I104" s="3" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C105" s="2">
-        <v>3</v>
-      </c>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
       <c r="D105" s="2" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="F105" s="2">
-        <v>2</v>
-      </c>
-      <c r="G105" s="2">
-        <v>8</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
       <c r="I105" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C106" s="2">
-        <v>3</v>
-      </c>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
       <c r="D106" s="2" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="F106" s="2">
-        <v>2</v>
-      </c>
-      <c r="G106" s="2">
-        <v>8</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
       <c r="I106" s="3" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:9">
       <c r="A107" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C107" s="2">
-        <v>3</v>
-      </c>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
       <c r="D107" s="2" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="F107" s="2">
-        <v>2</v>
-      </c>
-      <c r="G107" s="2">
-        <v>8</v>
-      </c>
-      <c r="H107" s="2" t="s">
         <v>228</v>
       </c>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2"/>
       <c r="I107" s="3" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="108" spans="1:9">
       <c r="A108" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C108" s="2">
-        <v>3</v>
-      </c>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
       <c r="D108" s="2" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="F108" s="2">
-        <v>2</v>
-      </c>
-      <c r="G108" s="2">
-        <v>8</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2"/>
       <c r="I108" s="3" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="109" spans="1:9">
       <c r="A109" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C109" s="2">
-        <v>3</v>
-      </c>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
       <c r="D109" s="2" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F109" s="2">
-        <v>2</v>
-      </c>
-      <c r="G109" s="2">
-        <v>8</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+      <c r="H109" s="2"/>
       <c r="I109" s="3" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C110" s="2">
-        <v>3</v>
-      </c>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
       <c r="D110" s="2" t="s">
-        <v>128</v>
+        <v>24</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="F110" s="2">
-        <v>2</v>
-      </c>
-      <c r="G110" s="2">
-        <v>8</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2"/>
       <c r="I110" s="3" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C111" s="2">
-        <v>3</v>
-      </c>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
       <c r="D111" s="2" t="s">
-        <v>128</v>
+        <v>24</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="F111" s="2">
-        <v>2</v>
-      </c>
-      <c r="G111" s="2">
-        <v>8</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
+      <c r="H111" s="2"/>
       <c r="I111" s="3" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C112" s="2">
-        <v>3</v>
-      </c>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
       <c r="D112" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="F112" s="2">
-        <v>2</v>
-      </c>
-      <c r="G112" s="2">
-        <v>8</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
+      <c r="H112" s="2"/>
       <c r="I112" s="3" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C113" s="2">
-        <v>3</v>
-      </c>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
       <c r="D113" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="F113" s="2">
-        <v>2</v>
-      </c>
-      <c r="G113" s="2">
-        <v>8</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="F113" s="2"/>
+      <c r="G113" s="2"/>
+      <c r="H113" s="2"/>
       <c r="I113" s="3" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C114" s="2">
-        <v>3</v>
-      </c>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
       <c r="D114" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F114" s="2">
-        <v>2</v>
-      </c>
-      <c r="G114" s="2">
-        <v>8</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="F114" s="2"/>
+      <c r="G114" s="2"/>
+      <c r="H114" s="2"/>
       <c r="I114" s="3" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C115" s="2">
-        <v>3</v>
-      </c>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
       <c r="D115" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="F115" s="2">
-        <v>2</v>
-      </c>
-      <c r="G115" s="2">
-        <v>8</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="F115" s="2"/>
+      <c r="G115" s="2"/>
+      <c r="H115" s="2"/>
       <c r="I115" s="3" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C116" s="2">
-        <v>3</v>
-      </c>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
       <c r="D116" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="F116" s="2">
-        <v>2</v>
-      </c>
-      <c r="G116" s="2">
-        <v>8</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="F116" s="2"/>
+      <c r="G116" s="2"/>
+      <c r="H116" s="2"/>
       <c r="I116" s="3" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B117" s="2"/>
-      <c r="C117" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C117" s="2">
+        <v>1</v>
+      </c>
       <c r="D117" s="2" t="s">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
-      <c r="H117" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="F117" s="2">
+        <v>2</v>
+      </c>
+      <c r="G117" s="2">
+        <v>10</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I117" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C118" s="2">
+        <v>1</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F118" s="2">
+        <v>2</v>
+      </c>
+      <c r="G118" s="2">
+        <v>10</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="I118" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="B118" s="2"/>
-      <c r="C118" s="2"/>
-      <c r="D118" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-      <c r="H118" s="2"/>
-      <c r="I118" s="3" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B119" s="2"/>
-      <c r="C119" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C119" s="2">
+        <v>1</v>
+      </c>
       <c r="D119" s="2" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="F119" s="2"/>
-      <c r="G119" s="2"/>
-      <c r="H119" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="F119" s="2">
+        <v>2</v>
+      </c>
+      <c r="G119" s="2">
+        <v>10</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I119" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B120" s="2"/>
-      <c r="C120" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C120" s="2">
+        <v>1</v>
+      </c>
       <c r="D120" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="F120" s="2"/>
-      <c r="G120" s="2"/>
-      <c r="H120" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="F120" s="2">
+        <v>2</v>
+      </c>
+      <c r="G120" s="2">
+        <v>10</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I120" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B121" s="2"/>
-      <c r="C121" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C121" s="2">
+        <v>1</v>
+      </c>
       <c r="D121" s="2" t="s">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
-      <c r="H121" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="F121" s="2">
+        <v>2</v>
+      </c>
+      <c r="G121" s="2">
+        <v>10</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I121" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="122" spans="1:9">
       <c r="A122" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B122" s="2"/>
-      <c r="C122" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C122" s="2">
+        <v>1</v>
+      </c>
       <c r="D122" s="2" t="s">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="F122" s="2"/>
-      <c r="G122" s="2"/>
-      <c r="H122" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="F122" s="2">
+        <v>2</v>
+      </c>
+      <c r="G122" s="2">
+        <v>10</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I122" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="123" spans="1:9">
       <c r="A123" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B123" s="2"/>
-      <c r="C123" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C123" s="2">
+        <v>1</v>
+      </c>
       <c r="D123" s="2" t="s">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="F123" s="2"/>
-      <c r="G123" s="2"/>
-      <c r="H123" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="F123" s="2">
+        <v>2</v>
+      </c>
+      <c r="G123" s="2">
+        <v>10</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I123" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="124" spans="1:9">
       <c r="A124" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B124" s="2"/>
-      <c r="C124" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C124" s="2">
+        <v>1</v>
+      </c>
       <c r="D124" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="F124" s="2"/>
-      <c r="G124" s="2"/>
-      <c r="H124" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="F124" s="2">
+        <v>2</v>
+      </c>
+      <c r="G124" s="2">
+        <v>10</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I124" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="125" spans="1:9">
       <c r="A125" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B125" s="2"/>
-      <c r="C125" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C125" s="2">
+        <v>1</v>
+      </c>
       <c r="D125" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="F125" s="2"/>
-      <c r="G125" s="2"/>
-      <c r="H125" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="F125" s="2">
+        <v>2</v>
+      </c>
+      <c r="G125" s="2">
+        <v>10</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I125" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="126" spans="1:9">
       <c r="A126" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B126" s="2"/>
-      <c r="C126" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C126" s="2">
+        <v>1</v>
+      </c>
       <c r="D126" s="2" t="s">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="F126" s="2"/>
-      <c r="G126" s="2"/>
-      <c r="H126" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="F126" s="2">
+        <v>2</v>
+      </c>
+      <c r="G126" s="2">
+        <v>10</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I126" s="3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="127" spans="1:9">
       <c r="A127" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B127" s="2"/>
-      <c r="C127" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C127" s="2">
+        <v>1</v>
+      </c>
       <c r="D127" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="F127" s="2"/>
-      <c r="G127" s="2"/>
-      <c r="H127" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="F127" s="2">
+        <v>2</v>
+      </c>
+      <c r="G127" s="2">
+        <v>10</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I127" s="3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="128" spans="1:9">
       <c r="A128" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B128" s="2"/>
-      <c r="C128" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C128" s="2">
+        <v>1</v>
+      </c>
       <c r="D128" s="2" t="s">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="F128" s="2"/>
-      <c r="G128" s="2"/>
-      <c r="H128" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="F128" s="2">
+        <v>2</v>
+      </c>
+      <c r="G128" s="2">
+        <v>10</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I128" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="129" spans="1:11">
       <c r="A129" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B129" s="2"/>
-      <c r="C129" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C129" s="2">
+        <v>1</v>
+      </c>
       <c r="D129" s="2" t="s">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="F129" s="2"/>
-      <c r="G129" s="2"/>
-      <c r="H129" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="F129" s="2">
+        <v>2</v>
+      </c>
+      <c r="G129" s="2">
+        <v>10</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I129" s="3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="130" spans="1:11">
       <c r="A130" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B130" s="2"/>
-      <c r="C130" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C130" s="2">
+        <v>1</v>
+      </c>
       <c r="D130" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="F130" s="2"/>
-      <c r="G130" s="2"/>
-      <c r="H130" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="F130" s="2">
+        <v>2</v>
+      </c>
+      <c r="G130" s="2">
+        <v>10</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I130" s="3" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="131" spans="1:11">
       <c r="A131" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B131" s="2"/>
-      <c r="C131" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C131" s="2">
+        <v>1</v>
+      </c>
       <c r="D131" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="F131" s="2"/>
-      <c r="G131" s="2"/>
-      <c r="H131" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="F131" s="2">
+        <v>2</v>
+      </c>
+      <c r="G131" s="2">
+        <v>10</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I131" s="3" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="132" spans="1:11">
       <c r="A132" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B132" s="2"/>
-      <c r="C132" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C132" s="2">
+        <v>1</v>
+      </c>
       <c r="D132" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="F132" s="2"/>
-      <c r="G132" s="2"/>
-      <c r="H132" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="F132" s="2">
+        <v>2</v>
+      </c>
+      <c r="G132" s="2">
+        <v>10</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I132" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B133" s="2"/>
-      <c r="C133" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C133" s="2">
+        <v>1</v>
+      </c>
       <c r="D133" s="2" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="F133" s="2"/>
-      <c r="G133" s="2"/>
-      <c r="H133" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="F133" s="2">
+        <v>2</v>
+      </c>
+      <c r="G133" s="2">
+        <v>10</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I133" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="134" spans="1:11">
       <c r="A134" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B134" s="2"/>
-      <c r="C134" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C134" s="2">
+        <v>1</v>
+      </c>
       <c r="D134" s="2" t="s">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="F134" s="2"/>
-      <c r="G134" s="2"/>
-      <c r="H134" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="F134" s="2">
+        <v>2</v>
+      </c>
+      <c r="G134" s="2">
+        <v>10</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I134" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="135" spans="1:11">
       <c r="A135" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B135" s="2"/>
-      <c r="C135" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C135" s="2">
+        <v>1</v>
+      </c>
       <c r="D135" s="2" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F135" s="2"/>
-      <c r="G135" s="2"/>
-      <c r="H135" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="F135" s="2">
+        <v>2</v>
+      </c>
+      <c r="G135" s="2">
+        <v>10</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I135" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="136" spans="1:11">
       <c r="A136" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B136" s="2"/>
-      <c r="C136" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C136" s="2">
+        <v>1</v>
+      </c>
       <c r="D136" s="2" t="s">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="F136" s="2"/>
-      <c r="G136" s="2"/>
-      <c r="H136" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="F136" s="2">
+        <v>2</v>
+      </c>
+      <c r="G136" s="2">
+        <v>10</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I136" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="137" spans="1:11">
       <c r="A137" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B137" s="2"/>
-      <c r="C137" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C137" s="2">
+        <v>1</v>
+      </c>
       <c r="D137" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="F137" s="2"/>
-      <c r="G137" s="2"/>
-      <c r="H137" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="F137" s="2">
+        <v>2</v>
+      </c>
+      <c r="G137" s="2">
+        <v>10</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I137" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="138" spans="1:11">
       <c r="A138" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B138" s="2"/>
-      <c r="C138" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C138" s="2">
+        <v>1</v>
+      </c>
       <c r="D138" s="2" t="s">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="F138" s="2"/>
-      <c r="G138" s="2"/>
-      <c r="H138" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="F138" s="2">
+        <v>2</v>
+      </c>
+      <c r="G138" s="2">
+        <v>10</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I138" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J138" s="2"/>
       <c r="K138" s="2"/>
     </row>
     <row r="139" spans="1:11">
       <c r="A139" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B139" s="2"/>
-      <c r="C139" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C139" s="2">
+        <v>1</v>
+      </c>
       <c r="D139" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="F139" s="2"/>
-      <c r="G139" s="2"/>
-      <c r="H139" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="F139" s="2">
+        <v>2</v>
+      </c>
+      <c r="G139" s="2">
+        <v>10</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I139" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J139" s="2"/>
       <c r="K139" s="2"/>
     </row>
     <row r="140" spans="1:11">
       <c r="A140" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B140" s="2"/>
-      <c r="C140" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C140" s="2">
+        <v>1</v>
+      </c>
       <c r="D140" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="F140" s="2"/>
-      <c r="G140" s="2"/>
-      <c r="H140" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="F140" s="2">
+        <v>2</v>
+      </c>
+      <c r="G140" s="2">
+        <v>10</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I140" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="J140" s="2"/>
       <c r="K140" s="2"/>
     </row>
     <row r="141" spans="1:11">
       <c r="A141" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B141" s="2"/>
-      <c r="C141" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C141" s="2">
+        <v>2</v>
+      </c>
       <c r="D141" s="2" t="s">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="E141" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="F141" s="2">
+        <v>2</v>
+      </c>
+      <c r="G141" s="2">
+        <v>8</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I141" s="3" t="s">
         <v>303</v>
-      </c>
-      <c r="F141" s="2"/>
-      <c r="G141" s="2"/>
-      <c r="H141" s="2"/>
-      <c r="I141" s="3" t="s">
-        <v>304</v>
       </c>
       <c r="J141" s="2"/>
       <c r="K141" s="2"/>
     </row>
     <row r="142" spans="1:11">
       <c r="A142" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B142" s="2"/>
-      <c r="C142" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C142" s="2">
+        <v>2</v>
+      </c>
       <c r="D142" s="2" t="s">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="E142" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="F142" s="2">
+        <v>2</v>
+      </c>
+      <c r="G142" s="2">
+        <v>8</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I142" s="3" t="s">
         <v>305</v>
-      </c>
-      <c r="F142" s="2"/>
-      <c r="G142" s="2"/>
-      <c r="H142" s="2"/>
-      <c r="I142" s="3" t="s">
-        <v>306</v>
       </c>
       <c r="J142" s="2"/>
       <c r="K142" s="2"/>
     </row>
     <row r="143" spans="1:11">
       <c r="A143" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B143" s="2"/>
-      <c r="C143" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C143" s="2">
+        <v>2</v>
+      </c>
       <c r="D143" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E143" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="F143" s="2">
+        <v>2</v>
+      </c>
+      <c r="G143" s="2">
+        <v>8</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I143" s="3" t="s">
         <v>307</v>
-      </c>
-      <c r="F143" s="2"/>
-      <c r="G143" s="2"/>
-      <c r="H143" s="2"/>
-      <c r="I143" s="3" t="s">
-        <v>308</v>
       </c>
       <c r="J143" s="2"/>
       <c r="K143" s="2"/>
     </row>
     <row r="144" spans="1:11">
       <c r="A144" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B144" s="2"/>
-      <c r="C144" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C144" s="2">
+        <v>2</v>
+      </c>
       <c r="D144" s="2" t="s">
-        <v>29</v>
+        <v>133</v>
       </c>
       <c r="E144" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F144" s="2">
+        <v>2</v>
+      </c>
+      <c r="G144" s="2">
+        <v>8</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I144" s="3" t="s">
         <v>309</v>
-      </c>
-      <c r="F144" s="2"/>
-      <c r="G144" s="2"/>
-      <c r="H144" s="2"/>
-      <c r="I144" s="3" t="s">
-        <v>310</v>
       </c>
       <c r="J144" s="2"/>
       <c r="K144" s="2"/>
     </row>
     <row r="145" spans="1:11">
       <c r="A145" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B145" s="2"/>
-      <c r="C145" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C145" s="2">
+        <v>2</v>
+      </c>
       <c r="D145" s="2" t="s">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="E145" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="F145" s="2">
+        <v>2</v>
+      </c>
+      <c r="G145" s="2">
+        <v>8</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I145" s="3" t="s">
         <v>311</v>
-      </c>
-      <c r="F145" s="2"/>
-      <c r="G145" s="2"/>
-      <c r="H145" s="2"/>
-      <c r="I145" s="3" t="s">
-        <v>312</v>
       </c>
       <c r="J145" s="2"/>
       <c r="K145" s="2"/>
     </row>
     <row r="146" spans="1:11">
       <c r="A146" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B146" s="2"/>
-      <c r="C146" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C146" s="2">
+        <v>2</v>
+      </c>
       <c r="D146" s="2" t="s">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="E146" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="F146" s="2">
+        <v>2</v>
+      </c>
+      <c r="G146" s="2">
+        <v>8</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I146" s="3" t="s">
         <v>313</v>
-      </c>
-      <c r="F146" s="2"/>
-      <c r="G146" s="2"/>
-      <c r="H146" s="2"/>
-      <c r="I146" s="3" t="s">
-        <v>314</v>
       </c>
       <c r="J146" s="2"/>
       <c r="K146" s="2"/>
     </row>
     <row r="147" spans="1:11">
       <c r="A147" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B147" s="2"/>
-      <c r="C147" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C147" s="2">
+        <v>2</v>
+      </c>
       <c r="D147" s="2" t="s">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="E147" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F147" s="2">
+        <v>2</v>
+      </c>
+      <c r="G147" s="2">
+        <v>8</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I147" s="3" t="s">
         <v>315</v>
-      </c>
-      <c r="F147" s="2"/>
-      <c r="G147" s="2"/>
-      <c r="H147" s="2"/>
-      <c r="I147" s="3" t="s">
-        <v>316</v>
       </c>
       <c r="J147" s="2"/>
       <c r="K147" s="2"/>
     </row>
     <row r="148" spans="1:11">
       <c r="A148" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B148" s="2"/>
-      <c r="C148" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C148" s="2">
+        <v>2</v>
+      </c>
       <c r="D148" s="2" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E148" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F148" s="2">
+        <v>2</v>
+      </c>
+      <c r="G148" s="2">
+        <v>8</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I148" s="3" t="s">
         <v>317</v>
-      </c>
-      <c r="F148" s="2"/>
-      <c r="G148" s="2"/>
-      <c r="H148" s="2"/>
-      <c r="I148" s="3" t="s">
-        <v>318</v>
       </c>
       <c r="J148" s="2"/>
       <c r="K148" s="2"/>
     </row>
     <row r="149" spans="1:11">
       <c r="A149" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B149" s="2"/>
-      <c r="C149" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C149" s="2">
+        <v>2</v>
+      </c>
       <c r="D149" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E149" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="F149" s="2">
+        <v>2</v>
+      </c>
+      <c r="G149" s="2">
+        <v>8</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I149" s="3" t="s">
         <v>319</v>
-      </c>
-      <c r="F149" s="2"/>
-      <c r="G149" s="2"/>
-      <c r="H149" s="2"/>
-      <c r="I149" s="3" t="s">
-        <v>320</v>
       </c>
       <c r="J149" s="2"/>
       <c r="K149" s="2"/>
     </row>
     <row r="150" spans="1:11">
       <c r="A150" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B150" s="2"/>
-      <c r="C150" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C150" s="2">
+        <v>2</v>
+      </c>
       <c r="D150" s="2" t="s">
-        <v>29</v>
+        <v>133</v>
       </c>
       <c r="E150" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="F150" s="2">
+        <v>2</v>
+      </c>
+      <c r="G150" s="2">
+        <v>8</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I150" s="3" t="s">
         <v>321</v>
-      </c>
-      <c r="F150" s="2"/>
-      <c r="G150" s="2"/>
-      <c r="H150" s="2"/>
-      <c r="I150" s="3" t="s">
-        <v>322</v>
       </c>
       <c r="J150" s="2"/>
       <c r="K150" s="2"/>
     </row>
     <row r="151" spans="1:11">
       <c r="A151" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B151" s="2"/>
-      <c r="C151" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C151" s="2">
+        <v>2</v>
+      </c>
       <c r="D151" s="2" t="s">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="E151" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="F151" s="2">
+        <v>2</v>
+      </c>
+      <c r="G151" s="2">
+        <v>8</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I151" s="3" t="s">
         <v>323</v>
-      </c>
-      <c r="F151" s="2"/>
-      <c r="G151" s="2"/>
-      <c r="H151" s="2"/>
-      <c r="I151" s="3" t="s">
-        <v>324</v>
       </c>
       <c r="J151" s="2"/>
       <c r="K151" s="2"/>
     </row>
     <row r="152" spans="1:11">
       <c r="A152" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B152" s="2"/>
-      <c r="C152" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C152" s="2">
+        <v>2</v>
+      </c>
       <c r="D152" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E152" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="F152" s="2">
+        <v>2</v>
+      </c>
+      <c r="G152" s="2">
+        <v>8</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I152" s="3" t="s">
         <v>325</v>
-      </c>
-      <c r="F152" s="2"/>
-      <c r="G152" s="2"/>
-      <c r="H152" s="2"/>
-      <c r="I152" s="3" t="s">
-        <v>326</v>
       </c>
       <c r="J152" s="2"/>
       <c r="K152" s="2"/>
     </row>
     <row r="153" spans="1:11">
       <c r="A153" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B153" s="2"/>
-      <c r="C153" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C153" s="2">
+        <v>2</v>
+      </c>
       <c r="D153" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E153" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="F153" s="2">
+        <v>2</v>
+      </c>
+      <c r="G153" s="2">
+        <v>8</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I153" s="3" t="s">
         <v>327</v>
-      </c>
-      <c r="F153" s="2"/>
-      <c r="G153" s="2"/>
-      <c r="H153" s="2"/>
-      <c r="I153" s="3" t="s">
-        <v>328</v>
       </c>
       <c r="J153" s="2"/>
       <c r="K153" s="2"/>
     </row>
     <row r="154" spans="1:11">
       <c r="A154" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B154" s="2"/>
-      <c r="C154" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C154" s="2">
+        <v>2</v>
+      </c>
       <c r="D154" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E154" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F154" s="2">
+        <v>2</v>
+      </c>
+      <c r="G154" s="2">
+        <v>8</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I154" s="3" t="s">
         <v>329</v>
-      </c>
-      <c r="F154" s="2"/>
-      <c r="G154" s="2"/>
-      <c r="H154" s="2"/>
-      <c r="I154" s="3" t="s">
-        <v>330</v>
       </c>
       <c r="J154" s="2"/>
       <c r="K154" s="2"/>
     </row>
     <row r="155" spans="1:11">
       <c r="A155" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B155" s="2"/>
-      <c r="C155" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C155" s="2">
+        <v>2</v>
+      </c>
       <c r="D155" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E155" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="F155" s="2">
+        <v>2</v>
+      </c>
+      <c r="G155" s="2">
+        <v>8</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I155" s="3" t="s">
         <v>331</v>
-      </c>
-      <c r="F155" s="2"/>
-      <c r="G155" s="2"/>
-      <c r="H155" s="2"/>
-      <c r="I155" s="3" t="s">
-        <v>332</v>
       </c>
       <c r="J155" s="2"/>
       <c r="K155" s="2"/>
     </row>
     <row r="156" spans="1:11">
       <c r="A156" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B156" s="2"/>
-      <c r="C156" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C156" s="2">
+        <v>2</v>
+      </c>
       <c r="D156" s="2" t="s">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="E156" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="F156" s="2">
+        <v>2</v>
+      </c>
+      <c r="G156" s="2">
+        <v>8</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I156" s="3" t="s">
         <v>333</v>
-      </c>
-      <c r="F156" s="2"/>
-      <c r="G156" s="2"/>
-      <c r="H156" s="2"/>
-      <c r="I156" s="3" t="s">
-        <v>334</v>
       </c>
       <c r="J156" s="2"/>
       <c r="K156" s="2"/>
     </row>
     <row r="157" spans="1:11">
       <c r="A157" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B157" s="2"/>
-      <c r="C157" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C157" s="2">
+        <v>2</v>
+      </c>
       <c r="D157" s="2" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E157" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="F157" s="2">
+        <v>2</v>
+      </c>
+      <c r="G157" s="2">
+        <v>8</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I157" s="3" t="s">
         <v>335</v>
-      </c>
-      <c r="F157" s="2"/>
-      <c r="G157" s="2"/>
-      <c r="H157" s="2"/>
-      <c r="I157" s="3" t="s">
-        <v>336</v>
       </c>
       <c r="J157" s="2"/>
       <c r="K157" s="2"/>
     </row>
     <row r="158" spans="1:11">
       <c r="A158" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B158" s="2"/>
-      <c r="C158" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C158" s="2">
+        <v>2</v>
+      </c>
       <c r="D158" s="2" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E158" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="F158" s="2">
+        <v>2</v>
+      </c>
+      <c r="G158" s="2">
+        <v>8</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I158" s="3" t="s">
         <v>337</v>
-      </c>
-      <c r="F158" s="2"/>
-      <c r="G158" s="2"/>
-      <c r="H158" s="2"/>
-      <c r="I158" s="3" t="s">
-        <v>338</v>
       </c>
       <c r="J158" s="2"/>
       <c r="K158" s="2"/>
     </row>
     <row r="159" spans="1:11">
       <c r="A159" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B159" s="2"/>
-      <c r="C159" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C159" s="2">
+        <v>2</v>
+      </c>
       <c r="D159" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E159" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="F159" s="2">
+        <v>2</v>
+      </c>
+      <c r="G159" s="2">
+        <v>8</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I159" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="F159" s="2"/>
-      <c r="G159" s="2"/>
-      <c r="H159" s="2"/>
-      <c r="I159" s="3" t="s">
-        <v>340</v>
       </c>
       <c r="J159" s="2"/>
       <c r="K159" s="2"/>
     </row>
     <row r="160" spans="1:11">
       <c r="A160" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B160" s="2"/>
-      <c r="C160" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C160" s="2">
+        <v>2</v>
+      </c>
       <c r="D160" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E160" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="F160" s="2">
+        <v>2</v>
+      </c>
+      <c r="G160" s="2">
+        <v>8</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I160" s="3" t="s">
         <v>341</v>
-      </c>
-      <c r="F160" s="2"/>
-      <c r="G160" s="2"/>
-      <c r="H160" s="2"/>
-      <c r="I160" s="3" t="s">
-        <v>342</v>
       </c>
       <c r="J160" s="2"/>
       <c r="K160" s="2"/>
     </row>
     <row r="161" spans="1:11">
       <c r="A161" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B161" s="2"/>
-      <c r="C161" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C161" s="2">
+        <v>2</v>
+      </c>
       <c r="D161" s="2" t="s">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="E161" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="F161" s="2">
+        <v>2</v>
+      </c>
+      <c r="G161" s="2">
+        <v>8</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I161" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="F161" s="2"/>
-      <c r="G161" s="2"/>
-      <c r="H161" s="2"/>
-      <c r="I161" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="J161" s="2"/>
       <c r="K161" s="2"/>
     </row>
     <row r="162" spans="1:11">
       <c r="A162" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B162" s="2"/>
-      <c r="C162" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C162" s="2">
+        <v>2</v>
+      </c>
       <c r="D162" s="2" t="s">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="E162" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="F162" s="2">
+        <v>2</v>
+      </c>
+      <c r="G162" s="2">
+        <v>8</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I162" s="3" t="s">
         <v>345</v>
-      </c>
-      <c r="F162" s="2"/>
-      <c r="G162" s="2"/>
-      <c r="H162" s="2"/>
-      <c r="I162" s="3" t="s">
-        <v>346</v>
       </c>
       <c r="J162" s="2"/>
       <c r="K162" s="2"/>
     </row>
     <row r="163" spans="1:11">
       <c r="A163" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B163" s="2"/>
-      <c r="C163" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C163" s="2">
+        <v>2</v>
+      </c>
       <c r="D163" s="2" t="s">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="E163" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F163" s="2">
+        <v>2</v>
+      </c>
+      <c r="G163" s="2">
+        <v>8</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I163" s="3" t="s">
         <v>347</v>
-      </c>
-      <c r="F163" s="2"/>
-      <c r="G163" s="2"/>
-      <c r="H163" s="2"/>
-      <c r="I163" s="3" t="s">
-        <v>348</v>
       </c>
       <c r="J163" s="2"/>
       <c r="K163" s="2"/>
     </row>
     <row r="164" spans="1:11">
       <c r="A164" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B164" s="2"/>
-      <c r="C164" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C164" s="2">
+        <v>3</v>
+      </c>
       <c r="D164" s="2" t="s">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="E164" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="F164" s="2">
+        <v>2</v>
+      </c>
+      <c r="G164" s="2">
+        <v>8</v>
+      </c>
+      <c r="H164" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="F164" s="2"/>
-      <c r="G164" s="2"/>
-      <c r="H164" s="2"/>
       <c r="I164" s="3" t="s">
         <v>350</v>
       </c>
@@ -5635,19 +5515,29 @@
     </row>
     <row r="165" spans="1:11">
       <c r="A165" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B165" s="2"/>
-      <c r="C165" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C165" s="2">
+        <v>3</v>
+      </c>
       <c r="D165" s="2" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="F165" s="2"/>
-      <c r="G165" s="2"/>
-      <c r="H165" s="2"/>
+      <c r="F165" s="2">
+        <v>2</v>
+      </c>
+      <c r="G165" s="2">
+        <v>8</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="I165" s="3" t="s">
         <v>352</v>
       </c>
@@ -5656,19 +5546,29 @@
     </row>
     <row r="166" spans="1:11">
       <c r="A166" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B166" s="2"/>
-      <c r="C166" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C166" s="2">
+        <v>3</v>
+      </c>
       <c r="D166" s="2" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="F166" s="2"/>
-      <c r="G166" s="2"/>
-      <c r="H166" s="2"/>
+      <c r="F166" s="2">
+        <v>2</v>
+      </c>
+      <c r="G166" s="2">
+        <v>8</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="I166" s="3" t="s">
         <v>354</v>
       </c>
@@ -5677,19 +5577,29 @@
     </row>
     <row r="167" spans="1:11">
       <c r="A167" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B167" s="2"/>
-      <c r="C167" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C167" s="2">
+        <v>3</v>
+      </c>
       <c r="D167" s="2" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="F167" s="2"/>
-      <c r="G167" s="2"/>
-      <c r="H167" s="2"/>
+      <c r="F167" s="2">
+        <v>2</v>
+      </c>
+      <c r="G167" s="2">
+        <v>8</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="I167" s="3" t="s">
         <v>356</v>
       </c>
@@ -5698,19 +5608,29 @@
     </row>
     <row r="168" spans="1:11">
       <c r="A168" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B168" s="2"/>
-      <c r="C168" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C168" s="2">
+        <v>3</v>
+      </c>
       <c r="D168" s="2" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F168" s="2"/>
-      <c r="G168" s="2"/>
-      <c r="H168" s="2"/>
+      <c r="F168" s="2">
+        <v>2</v>
+      </c>
+      <c r="G168" s="2">
+        <v>8</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="I168" s="3" t="s">
         <v>358</v>
       </c>
@@ -5719,19 +5639,29 @@
     </row>
     <row r="169" spans="1:11">
       <c r="A169" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B169" s="2"/>
-      <c r="C169" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C169" s="2">
+        <v>3</v>
+      </c>
       <c r="D169" s="2" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="F169" s="2"/>
-      <c r="G169" s="2"/>
-      <c r="H169" s="2"/>
+      <c r="F169" s="2">
+        <v>2</v>
+      </c>
+      <c r="G169" s="2">
+        <v>8</v>
+      </c>
+      <c r="H169" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="I169" s="3" t="s">
         <v>360</v>
       </c>
@@ -5740,19 +5670,29 @@
     </row>
     <row r="170" spans="1:11">
       <c r="A170" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B170" s="2"/>
-      <c r="C170" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C170" s="2">
+        <v>3</v>
+      </c>
       <c r="D170" s="2" t="s">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="F170" s="2"/>
-      <c r="G170" s="2"/>
-      <c r="H170" s="2"/>
+      <c r="F170" s="2">
+        <v>2</v>
+      </c>
+      <c r="G170" s="2">
+        <v>8</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="I170" s="3" t="s">
         <v>362</v>
       </c>
@@ -5761,19 +5701,29 @@
     </row>
     <row r="171" spans="1:11">
       <c r="A171" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B171" s="2"/>
-      <c r="C171" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C171" s="2">
+        <v>3</v>
+      </c>
       <c r="D171" s="2" t="s">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="F171" s="2"/>
-      <c r="G171" s="2"/>
-      <c r="H171" s="2"/>
+      <c r="F171" s="2">
+        <v>2</v>
+      </c>
+      <c r="G171" s="2">
+        <v>8</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="I171" s="3" t="s">
         <v>364</v>
       </c>
@@ -5782,114 +5732,164 @@
     </row>
     <row r="172" spans="1:11">
       <c r="A172" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B172" s="2"/>
-      <c r="C172" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C172" s="2">
+        <v>3</v>
+      </c>
       <c r="D172" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="F172" s="2"/>
-      <c r="G172" s="2"/>
-      <c r="H172" s="2"/>
+      <c r="F172" s="2">
+        <v>2</v>
+      </c>
+      <c r="G172" s="2">
+        <v>8</v>
+      </c>
+      <c r="H172" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="I172" s="3" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="173" spans="1:11">
       <c r="A173" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B173" s="2"/>
-      <c r="C173" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C173" s="2">
+        <v>3</v>
+      </c>
       <c r="D173" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="F173" s="2"/>
-      <c r="G173" s="2"/>
-      <c r="H173" s="2"/>
+      <c r="F173" s="2">
+        <v>2</v>
+      </c>
+      <c r="G173" s="2">
+        <v>8</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="I173" s="3" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="174" spans="1:11">
       <c r="A174" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B174" s="2"/>
-      <c r="C174" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C174" s="2">
+        <v>3</v>
+      </c>
       <c r="D174" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="F174" s="2"/>
-      <c r="G174" s="2"/>
-      <c r="H174" s="2"/>
+      <c r="F174" s="2">
+        <v>2</v>
+      </c>
+      <c r="G174" s="2">
+        <v>8</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="I174" s="3" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="175" spans="1:11">
       <c r="A175" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B175" s="2"/>
-      <c r="C175" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C175" s="2">
+        <v>3</v>
+      </c>
       <c r="D175" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="F175" s="2"/>
-      <c r="G175" s="2"/>
-      <c r="H175" s="2"/>
+      <c r="F175" s="2">
+        <v>2</v>
+      </c>
+      <c r="G175" s="2">
+        <v>8</v>
+      </c>
+      <c r="H175" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="I175" s="3" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="176" spans="1:11">
       <c r="A176" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B176" s="2"/>
-      <c r="C176" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C176" s="2">
+        <v>3</v>
+      </c>
       <c r="D176" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="F176" s="2"/>
-      <c r="G176" s="2"/>
-      <c r="H176" s="2"/>
+      <c r="F176" s="2">
+        <v>2</v>
+      </c>
+      <c r="G176" s="2">
+        <v>8</v>
+      </c>
+      <c r="H176" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="I176" s="3" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="177" spans="1:9">
       <c r="A177" s="2" t="s">
-        <v>126</v>
+        <v>248</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>127</v>
+        <v>249</v>
       </c>
       <c r="C177" s="2">
         <v>3</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>140</v>
+        <v>261</v>
       </c>
       <c r="F177" s="2">
         <v>2</v>
@@ -5898,27 +5898,27 @@
         <v>8</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>228</v>
+        <v>349</v>
       </c>
       <c r="I177" s="3" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
     </row>
     <row r="178" spans="1:9">
       <c r="A178" s="2" t="s">
-        <v>126</v>
+        <v>248</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>127</v>
+        <v>249</v>
       </c>
       <c r="C178" s="2">
         <v>3</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>142</v>
+        <v>263</v>
       </c>
       <c r="F178" s="2">
         <v>2</v>
@@ -5927,27 +5927,27 @@
         <v>8</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>228</v>
+        <v>349</v>
       </c>
       <c r="I178" s="3" t="s">
-        <v>143</v>
+        <v>264</v>
       </c>
     </row>
     <row r="179" spans="1:9">
       <c r="A179" s="2" t="s">
-        <v>126</v>
+        <v>248</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>127</v>
+        <v>249</v>
       </c>
       <c r="C179" s="2">
         <v>3</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>144</v>
+        <v>265</v>
       </c>
       <c r="F179" s="2">
         <v>2</v>
@@ -5956,27 +5956,27 @@
         <v>8</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>228</v>
+        <v>349</v>
       </c>
       <c r="I179" s="3" t="s">
-        <v>145</v>
+        <v>266</v>
       </c>
     </row>
     <row r="180" spans="1:9">
       <c r="A180" s="2" t="s">
-        <v>126</v>
+        <v>248</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>146</v>
+        <v>267</v>
       </c>
       <c r="C180" s="2">
         <v>3</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>151</v>
+        <v>272</v>
       </c>
       <c r="F180" s="2">
         <v>2</v>
@@ -5985,27 +5985,27 @@
         <v>8</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>228</v>
+        <v>349</v>
       </c>
       <c r="I180" s="3" t="s">
-        <v>152</v>
+        <v>273</v>
       </c>
     </row>
     <row r="181" spans="1:9">
       <c r="A181" s="2" t="s">
-        <v>126</v>
+        <v>248</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>146</v>
+        <v>267</v>
       </c>
       <c r="C181" s="2">
         <v>3</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>153</v>
+        <v>274</v>
       </c>
       <c r="F181" s="2">
         <v>2</v>
@@ -6014,27 +6014,27 @@
         <v>8</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>228</v>
+        <v>349</v>
       </c>
       <c r="I181" s="3" t="s">
-        <v>154</v>
+        <v>275</v>
       </c>
     </row>
     <row r="182" spans="1:9">
       <c r="A182" s="2" t="s">
-        <v>126</v>
+        <v>248</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>146</v>
+        <v>267</v>
       </c>
       <c r="C182" s="2">
         <v>3</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>155</v>
+        <v>276</v>
       </c>
       <c r="F182" s="2">
         <v>2</v>
@@ -6043,27 +6043,27 @@
         <v>8</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>228</v>
+        <v>349</v>
       </c>
       <c r="I182" s="3" t="s">
-        <v>156</v>
+        <v>277</v>
       </c>
     </row>
     <row r="183" spans="1:9">
       <c r="A183" s="2" t="s">
-        <v>126</v>
+        <v>248</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>146</v>
+        <v>267</v>
       </c>
       <c r="C183" s="2">
         <v>3</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>157</v>
+        <v>278</v>
       </c>
       <c r="F183" s="2">
         <v>2</v>
@@ -6072,27 +6072,27 @@
         <v>8</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>228</v>
+        <v>349</v>
       </c>
       <c r="I183" s="3" t="s">
-        <v>158</v>
+        <v>279</v>
       </c>
     </row>
     <row r="184" spans="1:9">
       <c r="A184" s="2" t="s">
-        <v>126</v>
+        <v>248</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>163</v>
+        <v>284</v>
       </c>
       <c r="C184" s="2">
         <v>3</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>215</v>
+        <v>336</v>
       </c>
       <c r="F184" s="2">
         <v>2</v>
@@ -6101,27 +6101,27 @@
         <v>8</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>228</v>
+        <v>349</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>216</v>
+        <v>337</v>
       </c>
     </row>
     <row r="185" spans="1:9">
       <c r="A185" s="2" t="s">
-        <v>126</v>
+        <v>248</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>163</v>
+        <v>284</v>
       </c>
       <c r="C185" s="2">
         <v>3</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>217</v>
+        <v>338</v>
       </c>
       <c r="F185" s="2">
         <v>2</v>
@@ -6130,27 +6130,27 @@
         <v>8</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>228</v>
+        <v>349</v>
       </c>
       <c r="I185" s="3" t="s">
-        <v>218</v>
+        <v>339</v>
       </c>
     </row>
     <row r="186" spans="1:9">
       <c r="A186" s="2" t="s">
-        <v>126</v>
+        <v>248</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>163</v>
+        <v>284</v>
       </c>
       <c r="C186" s="2">
         <v>3</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>219</v>
+        <v>340</v>
       </c>
       <c r="F186" s="2">
         <v>2</v>
@@ -6159,27 +6159,27 @@
         <v>8</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>228</v>
+        <v>349</v>
       </c>
       <c r="I186" s="3" t="s">
-        <v>220</v>
+        <v>341</v>
       </c>
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="2" t="s">
-        <v>126</v>
+        <v>248</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>163</v>
+        <v>284</v>
       </c>
       <c r="C187" s="2">
         <v>3</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>221</v>
+        <v>342</v>
       </c>
       <c r="F187" s="2">
         <v>2</v>
@@ -6188,10 +6188,10 @@
         <v>8</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>228</v>
+        <v>349</v>
       </c>
       <c r="I187" s="3" t="s">
-        <v>222</v>
+        <v>343</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -6583,7 +6583,7 @@
         <v>1</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>415</v>
@@ -6595,7 +6595,7 @@
         <v>12</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>130</v>
+        <v>251</v>
       </c>
       <c r="I206" s="3" t="s">
         <v>416</v>
@@ -6612,7 +6612,7 @@
         <v>1</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>417</v>
@@ -6624,7 +6624,7 @@
         <v>12</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>130</v>
+        <v>251</v>
       </c>
       <c r="I207" s="3" t="s">
         <v>418</v>
@@ -6641,7 +6641,7 @@
         <v>1</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>419</v>
@@ -6653,7 +6653,7 @@
         <v>12</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>130</v>
+        <v>251</v>
       </c>
       <c r="I208" s="3" t="s">
         <v>420</v>
@@ -6670,7 +6670,7 @@
         <v>1</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>421</v>
@@ -6682,7 +6682,7 @@
         <v>12</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>130</v>
+        <v>251</v>
       </c>
       <c r="I209" s="3" t="s">
         <v>422</v>
@@ -6699,7 +6699,7 @@
         <v>1</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>423</v>
@@ -6711,7 +6711,7 @@
         <v>12</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>130</v>
+        <v>251</v>
       </c>
       <c r="I210" s="3" t="s">
         <v>424</v>
@@ -6728,7 +6728,7 @@
         <v>1</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>425</v>
@@ -6740,7 +6740,7 @@
         <v>12</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>130</v>
+        <v>251</v>
       </c>
       <c r="I211" s="3" t="s">
         <v>426</v>
@@ -6757,7 +6757,7 @@
         <v>1</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>427</v>
@@ -6769,7 +6769,7 @@
         <v>12</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>130</v>
+        <v>251</v>
       </c>
       <c r="I212" s="3" t="s">
         <v>428</v>
@@ -6786,7 +6786,7 @@
         <v>1</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>429</v>
@@ -6798,7 +6798,7 @@
         <v>12</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>130</v>
+        <v>251</v>
       </c>
       <c r="I213" s="3" t="s">
         <v>430</v>
@@ -6815,7 +6815,7 @@
         <v>1</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>431</v>
@@ -6827,7 +6827,7 @@
         <v>12</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>130</v>
+        <v>251</v>
       </c>
       <c r="I214" s="3" t="s">
         <v>432</v>
@@ -6844,7 +6844,7 @@
         <v>1</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>433</v>
@@ -6856,7 +6856,7 @@
         <v>12</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>130</v>
+        <v>251</v>
       </c>
       <c r="I215" s="3" t="s">
         <v>434</v>
@@ -6873,7 +6873,7 @@
         <v>2</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>435</v>
@@ -6900,7 +6900,7 @@
         <v>2</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>437</v>
@@ -6927,7 +6927,7 @@
         <v>2</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>439</v>
@@ -6954,7 +6954,7 @@
         <v>2</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>441</v>
@@ -6981,7 +6981,7 @@
         <v>2</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>443</v>
@@ -7008,7 +7008,7 @@
         <v>2</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>445</v>
@@ -7035,7 +7035,7 @@
         <v>2</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>447</v>
@@ -7062,7 +7062,7 @@
         <v>2</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>449</v>
@@ -7089,7 +7089,7 @@
         <v>3</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>451</v>
@@ -7116,7 +7116,7 @@
         <v>3</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>453</v>
@@ -7143,7 +7143,7 @@
         <v>3</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>455</v>
@@ -7170,7 +7170,7 @@
         <v>3</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>457</v>
@@ -7197,7 +7197,7 @@
         <v>3</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>459</v>
@@ -7224,7 +7224,7 @@
         <v>3</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>461</v>
@@ -7251,7 +7251,7 @@
         <v>3</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>463</v>
@@ -7278,7 +7278,7 @@
         <v>3</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>465</v>
@@ -7305,7 +7305,7 @@
         <v>4</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>467</v>
@@ -7332,7 +7332,7 @@
         <v>4</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>469</v>
@@ -7359,7 +7359,7 @@
         <v>4</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>471</v>
@@ -7386,7 +7386,7 @@
         <v>4</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>473</v>
@@ -7413,7 +7413,7 @@
         <v>4</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>475</v>
@@ -7440,7 +7440,7 @@
         <v>4</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>477</v>
@@ -7467,7 +7467,7 @@
         <v>4</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>479</v>
@@ -7494,7 +7494,7 @@
         <v>4</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>481</v>
@@ -7511,14 +7511,14 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I152">
-    <sortCondition ref="A2:A152"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I239">
+    <sortCondition ref="A2:A239"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="I220" r:id="rId1" xr:uid="{5FEEF02D-1341-4501-88A4-821F6FD7EF17}"/>
     <hyperlink ref="I212" r:id="rId2" xr:uid="{5A3DDB27-6AB2-4F01-A380-E2B2770C763C}"/>
-    <hyperlink ref="I59" r:id="rId3" xr:uid="{9A2E61CF-14C4-4C29-9CF8-0F94BA115C5A}"/>
-    <hyperlink ref="I72" r:id="rId4" xr:uid="{1770959C-0E29-49F6-AB71-FEB65B1CF5D7}"/>
+    <hyperlink ref="I119" r:id="rId3" xr:uid="{9A2E61CF-14C4-4C29-9CF8-0F94BA115C5A}"/>
+    <hyperlink ref="I132" r:id="rId4" xr:uid="{1770959C-0E29-49F6-AB71-FEB65B1CF5D7}"/>
     <hyperlink ref="I34" r:id="rId5" xr:uid="{19BDA2BA-2F24-44AE-B917-BCD6CDF1CFF4}"/>
     <hyperlink ref="I38" r:id="rId6" xr:uid="{7D3DFBC6-B116-451B-836B-8075186821B9}"/>
     <hyperlink ref="I17" r:id="rId7" xr:uid="{216845C6-6E68-4178-BF06-6D9C8E5C8AD9}"/>
@@ -7571,122 +7571,122 @@
     <hyperlink ref="I26" r:id="rId54" xr:uid="{B0834553-413A-447D-9BB5-1F90271B303E}"/>
     <hyperlink ref="I25" r:id="rId55" xr:uid="{EF394F86-2534-4AC1-8514-749DAB5ADB8A}"/>
     <hyperlink ref="I42" r:id="rId56" xr:uid="{6E96098B-92AD-4B76-ACC5-FBA433DE367C}"/>
-    <hyperlink ref="I146" r:id="rId57" xr:uid="{9088BFD3-F464-4EBD-8521-320F41C53B9C}"/>
+    <hyperlink ref="I86" r:id="rId57" xr:uid="{9088BFD3-F464-4EBD-8521-320F41C53B9C}"/>
     <hyperlink ref="I3" r:id="rId58" xr:uid="{209052D6-FF1D-4C04-A19D-AD7AB3C987FB}"/>
-    <hyperlink ref="I163" r:id="rId59" xr:uid="{E4A89E54-0D19-4F0E-9F59-3913758C63DC}"/>
-    <hyperlink ref="I118" r:id="rId60" xr:uid="{AC3447EC-DA60-4267-90E1-DD6DF3C5F08F}"/>
-    <hyperlink ref="I145" r:id="rId61" xr:uid="{B2630573-1E15-40D5-8E0F-47F03FC911E5}"/>
-    <hyperlink ref="I147" r:id="rId62" xr:uid="{0BFEB761-29A5-4BE5-B6E1-F0E465E6B484}"/>
-    <hyperlink ref="I162" r:id="rId63" xr:uid="{B9AB9C19-C485-43E9-BBFC-27EEDA09DAA9}"/>
-    <hyperlink ref="I129" r:id="rId64" xr:uid="{BC750D1B-B4A9-4B83-BC08-1A1BED73C083}"/>
-    <hyperlink ref="I117" r:id="rId65" xr:uid="{AFE44353-3912-4CF3-90C6-52D9F9E0F93D}"/>
-    <hyperlink ref="I156" r:id="rId66" xr:uid="{EDF0BCBD-F8C4-4EA6-A04F-3CE17BAB4DB4}"/>
-    <hyperlink ref="I151" r:id="rId67" xr:uid="{CCFF3EE7-1C98-4880-9238-078F9D4C409A}"/>
-    <hyperlink ref="I128" r:id="rId68" xr:uid="{1BF0E806-D633-4E2D-8754-2A97B3F9975F}"/>
-    <hyperlink ref="I144" r:id="rId69" xr:uid="{2104A4B1-0F16-47F1-9095-D5CCF62FE78A}"/>
-    <hyperlink ref="I150" r:id="rId70" xr:uid="{2E1DF1A0-4C18-4419-A129-F02A03F70A8D}"/>
-    <hyperlink ref="I126" r:id="rId71" xr:uid="{2098ACEB-90D3-4E58-9C75-8E9AF8D4B774}"/>
-    <hyperlink ref="I170" r:id="rId72" xr:uid="{36EDFAF9-83CE-466D-B43F-63FA8F187A3F}"/>
-    <hyperlink ref="I171" r:id="rId73" xr:uid="{F0FD34D7-A72A-4BB4-9B36-10867FB7BA8F}"/>
-    <hyperlink ref="I134" r:id="rId74" xr:uid="{4709E9FD-64DE-4B8F-AB8F-7A846AB38F23}"/>
-    <hyperlink ref="I138" r:id="rId75" xr:uid="{31268B26-F0C1-400B-A6C1-0F6AEA5E91AA}"/>
-    <hyperlink ref="I87" r:id="rId76" xr:uid="{823C3F5B-17BA-451A-9253-754D9D302392}"/>
-    <hyperlink ref="I142" r:id="rId77" xr:uid="{BB97EC60-F4DA-40CC-92D5-289EF1109D00}"/>
-    <hyperlink ref="I136" r:id="rId78" xr:uid="{E22262E8-7E9A-45C7-B3E3-6C0F219FC62E}"/>
-    <hyperlink ref="I164" r:id="rId79" xr:uid="{B511DB33-F88B-4F00-A8E7-587EA1D04B13}"/>
-    <hyperlink ref="I141" r:id="rId80" xr:uid="{A44DB231-48CF-4CA2-8DA8-BF74EA1ACF19}"/>
-    <hyperlink ref="I122" r:id="rId81" xr:uid="{E0EA6CB1-9B3D-4A73-8AB2-AA46A14B6E8D}"/>
-    <hyperlink ref="I123" r:id="rId82" xr:uid="{22697333-6420-46BE-85EE-0034998E4302}"/>
-    <hyperlink ref="I161" r:id="rId83" xr:uid="{42159EE5-751A-44A8-8164-644834513ACF}"/>
-    <hyperlink ref="I121" r:id="rId84" xr:uid="{38096343-3383-4A48-886C-53BC0E3F0D64}"/>
-    <hyperlink ref="I135" r:id="rId85" xr:uid="{B6BC2919-5D1A-45B3-8B57-C9888B74F398}"/>
-    <hyperlink ref="I119" r:id="rId86" xr:uid="{A7205A3E-E0D3-4866-A364-E1201808BD18}"/>
-    <hyperlink ref="I169" r:id="rId87" xr:uid="{5F00C7A4-33FF-44CC-8A1A-77111F9D6668}"/>
-    <hyperlink ref="I167" r:id="rId88" xr:uid="{DDB23DCE-80AC-4FD7-9DDD-ED21FB2F0E67}"/>
-    <hyperlink ref="I168" r:id="rId89" xr:uid="{005BF53A-6986-4512-9FF4-0A7AD06CF5EF}"/>
-    <hyperlink ref="I148" r:id="rId90" xr:uid="{966CF992-AD49-46D9-94F8-F1FDC79DDAAD}"/>
-    <hyperlink ref="I133" r:id="rId91" xr:uid="{7665310A-A649-4383-94CE-A3523E0FE9E6}"/>
-    <hyperlink ref="I158" r:id="rId92" xr:uid="{6522946F-5418-4751-99E4-CB7B79FD02F9}"/>
-    <hyperlink ref="I157" r:id="rId93" xr:uid="{497D711D-7DD9-489F-890D-955E2706DAB6}"/>
-    <hyperlink ref="I166" r:id="rId94" xr:uid="{876B3467-AF63-4603-87C1-0EF9F8919280}"/>
-    <hyperlink ref="I165" r:id="rId95" xr:uid="{BDD8CF61-5731-4058-ACDB-936E4AA296B0}"/>
-    <hyperlink ref="I57" r:id="rId96" xr:uid="{7FA5D50D-0A51-4C0E-80D3-C79C3FC42A74}"/>
-    <hyperlink ref="I60" r:id="rId97" xr:uid="{F2C2FC18-CEEC-4760-A24C-65EB79F9F55A}"/>
-    <hyperlink ref="I74" r:id="rId98" xr:uid="{EC6233B5-2BFE-4556-AA37-7736D2872A70}"/>
-    <hyperlink ref="I94" r:id="rId99" xr:uid="{C02CD575-F5EF-412E-8168-C6ABCDA870CD}"/>
-    <hyperlink ref="I65" r:id="rId100" xr:uid="{B62F0A3D-92B5-4A5B-AA5F-4226D7070C00}"/>
-    <hyperlink ref="I80" r:id="rId101" xr:uid="{73F689CB-CC64-41A7-8D24-C55C05E7C024}"/>
-    <hyperlink ref="I127" r:id="rId102" xr:uid="{5F47E355-299A-4AF8-B648-EF9D4FCD382C}"/>
-    <hyperlink ref="I115" r:id="rId103" xr:uid="{E947A4BC-A137-4184-B53C-40A7C3151604}"/>
-    <hyperlink ref="I88" r:id="rId104" xr:uid="{21B79518-E8BA-4923-884B-904E0E67C0E0}"/>
-    <hyperlink ref="I116" r:id="rId105" xr:uid="{FE4AA32F-0AC8-4C26-930E-BA8DE5F54C93}"/>
-    <hyperlink ref="I111" r:id="rId106" xr:uid="{15E95505-5C7B-4CC4-B245-0A093431B93C}"/>
-    <hyperlink ref="I107" r:id="rId107" xr:uid="{D747AFBB-9217-4F8F-8A01-17EF8ADC8DCC}"/>
-    <hyperlink ref="I112" r:id="rId108" xr:uid="{D3A1D224-F1AE-4ABC-9AA9-DE29A771196F}"/>
-    <hyperlink ref="I113" r:id="rId109" xr:uid="{A08BC7A9-AD14-4EBE-9122-2E68CBC67E2C}"/>
-    <hyperlink ref="I108" r:id="rId110" xr:uid="{FB94721C-B471-4FFC-94E3-E5FFB4C70F01}"/>
-    <hyperlink ref="I99" r:id="rId111" xr:uid="{150CB30D-CB02-4AC9-9051-241A21E88CDC}"/>
-    <hyperlink ref="I78" r:id="rId112" xr:uid="{A6B84085-FB9A-498B-AE4F-74A0C62F54A1}"/>
-    <hyperlink ref="I81" r:id="rId113" xr:uid="{53BEF60D-BF1D-48BC-934B-D23ED97F1DF2}"/>
-    <hyperlink ref="I89" r:id="rId114" xr:uid="{01A532C8-7B79-4FD1-8815-4CFFBAA5FC3A}"/>
-    <hyperlink ref="I63" r:id="rId115" xr:uid="{8F603BDF-34E8-4EB7-B9FA-CA2AEAEF7E18}"/>
+    <hyperlink ref="I103" r:id="rId59" xr:uid="{E4A89E54-0D19-4F0E-9F59-3913758C63DC}"/>
+    <hyperlink ref="I58" r:id="rId60" xr:uid="{AC3447EC-DA60-4267-90E1-DD6DF3C5F08F}"/>
+    <hyperlink ref="I85" r:id="rId61" xr:uid="{B2630573-1E15-40D5-8E0F-47F03FC911E5}"/>
+    <hyperlink ref="I87" r:id="rId62" xr:uid="{0BFEB761-29A5-4BE5-B6E1-F0E465E6B484}"/>
+    <hyperlink ref="I102" r:id="rId63" xr:uid="{B9AB9C19-C485-43E9-BBFC-27EEDA09DAA9}"/>
+    <hyperlink ref="I69" r:id="rId64" xr:uid="{BC750D1B-B4A9-4B83-BC08-1A1BED73C083}"/>
+    <hyperlink ref="I57" r:id="rId65" xr:uid="{AFE44353-3912-4CF3-90C6-52D9F9E0F93D}"/>
+    <hyperlink ref="I96" r:id="rId66" xr:uid="{EDF0BCBD-F8C4-4EA6-A04F-3CE17BAB4DB4}"/>
+    <hyperlink ref="I91" r:id="rId67" xr:uid="{CCFF3EE7-1C98-4880-9238-078F9D4C409A}"/>
+    <hyperlink ref="I68" r:id="rId68" xr:uid="{1BF0E806-D633-4E2D-8754-2A97B3F9975F}"/>
+    <hyperlink ref="I84" r:id="rId69" xr:uid="{2104A4B1-0F16-47F1-9095-D5CCF62FE78A}"/>
+    <hyperlink ref="I90" r:id="rId70" xr:uid="{2E1DF1A0-4C18-4419-A129-F02A03F70A8D}"/>
+    <hyperlink ref="I66" r:id="rId71" xr:uid="{2098ACEB-90D3-4E58-9C75-8E9AF8D4B774}"/>
+    <hyperlink ref="I110" r:id="rId72" xr:uid="{36EDFAF9-83CE-466D-B43F-63FA8F187A3F}"/>
+    <hyperlink ref="I111" r:id="rId73" xr:uid="{F0FD34D7-A72A-4BB4-9B36-10867FB7BA8F}"/>
+    <hyperlink ref="I74" r:id="rId74" xr:uid="{4709E9FD-64DE-4B8F-AB8F-7A846AB38F23}"/>
+    <hyperlink ref="I78" r:id="rId75" xr:uid="{31268B26-F0C1-400B-A6C1-0F6AEA5E91AA}"/>
+    <hyperlink ref="I147" r:id="rId76" xr:uid="{823C3F5B-17BA-451A-9253-754D9D302392}"/>
+    <hyperlink ref="I82" r:id="rId77" xr:uid="{BB97EC60-F4DA-40CC-92D5-289EF1109D00}"/>
+    <hyperlink ref="I76" r:id="rId78" xr:uid="{E22262E8-7E9A-45C7-B3E3-6C0F219FC62E}"/>
+    <hyperlink ref="I104" r:id="rId79" xr:uid="{B511DB33-F88B-4F00-A8E7-587EA1D04B13}"/>
+    <hyperlink ref="I81" r:id="rId80" xr:uid="{A44DB231-48CF-4CA2-8DA8-BF74EA1ACF19}"/>
+    <hyperlink ref="I62" r:id="rId81" xr:uid="{E0EA6CB1-9B3D-4A73-8AB2-AA46A14B6E8D}"/>
+    <hyperlink ref="I63" r:id="rId82" xr:uid="{22697333-6420-46BE-85EE-0034998E4302}"/>
+    <hyperlink ref="I101" r:id="rId83" xr:uid="{42159EE5-751A-44A8-8164-644834513ACF}"/>
+    <hyperlink ref="I61" r:id="rId84" xr:uid="{38096343-3383-4A48-886C-53BC0E3F0D64}"/>
+    <hyperlink ref="I75" r:id="rId85" xr:uid="{B6BC2919-5D1A-45B3-8B57-C9888B74F398}"/>
+    <hyperlink ref="I59" r:id="rId86" xr:uid="{A7205A3E-E0D3-4866-A364-E1201808BD18}"/>
+    <hyperlink ref="I109" r:id="rId87" xr:uid="{5F00C7A4-33FF-44CC-8A1A-77111F9D6668}"/>
+    <hyperlink ref="I107" r:id="rId88" xr:uid="{DDB23DCE-80AC-4FD7-9DDD-ED21FB2F0E67}"/>
+    <hyperlink ref="I108" r:id="rId89" xr:uid="{005BF53A-6986-4512-9FF4-0A7AD06CF5EF}"/>
+    <hyperlink ref="I88" r:id="rId90" xr:uid="{966CF992-AD49-46D9-94F8-F1FDC79DDAAD}"/>
+    <hyperlink ref="I73" r:id="rId91" xr:uid="{7665310A-A649-4383-94CE-A3523E0FE9E6}"/>
+    <hyperlink ref="I98" r:id="rId92" xr:uid="{6522946F-5418-4751-99E4-CB7B79FD02F9}"/>
+    <hyperlink ref="I97" r:id="rId93" xr:uid="{497D711D-7DD9-489F-890D-955E2706DAB6}"/>
+    <hyperlink ref="I106" r:id="rId94" xr:uid="{876B3467-AF63-4603-87C1-0EF9F8919280}"/>
+    <hyperlink ref="I105" r:id="rId95" xr:uid="{BDD8CF61-5731-4058-ACDB-936E4AA296B0}"/>
+    <hyperlink ref="I117" r:id="rId96" xr:uid="{7FA5D50D-0A51-4C0E-80D3-C79C3FC42A74}"/>
+    <hyperlink ref="I120" r:id="rId97" xr:uid="{F2C2FC18-CEEC-4760-A24C-65EB79F9F55A}"/>
+    <hyperlink ref="I134" r:id="rId98" xr:uid="{EC6233B5-2BFE-4556-AA37-7736D2872A70}"/>
+    <hyperlink ref="I154" r:id="rId99" xr:uid="{C02CD575-F5EF-412E-8168-C6ABCDA870CD}"/>
+    <hyperlink ref="I125" r:id="rId100" xr:uid="{B62F0A3D-92B5-4A5B-AA5F-4226D7070C00}"/>
+    <hyperlink ref="I140" r:id="rId101" xr:uid="{73F689CB-CC64-41A7-8D24-C55C05E7C024}"/>
+    <hyperlink ref="I67" r:id="rId102" xr:uid="{5F47E355-299A-4AF8-B648-EF9D4FCD382C}"/>
+    <hyperlink ref="I175" r:id="rId103" xr:uid="{E947A4BC-A137-4184-B53C-40A7C3151604}"/>
+    <hyperlink ref="I148" r:id="rId104" xr:uid="{21B79518-E8BA-4923-884B-904E0E67C0E0}"/>
+    <hyperlink ref="I176" r:id="rId105" xr:uid="{FE4AA32F-0AC8-4C26-930E-BA8DE5F54C93}"/>
+    <hyperlink ref="I171" r:id="rId106" xr:uid="{15E95505-5C7B-4CC4-B245-0A093431B93C}"/>
+    <hyperlink ref="I167" r:id="rId107" xr:uid="{D747AFBB-9217-4F8F-8A01-17EF8ADC8DCC}"/>
+    <hyperlink ref="I172" r:id="rId108" xr:uid="{D3A1D224-F1AE-4ABC-9AA9-DE29A771196F}"/>
+    <hyperlink ref="I173" r:id="rId109" xr:uid="{A08BC7A9-AD14-4EBE-9122-2E68CBC67E2C}"/>
+    <hyperlink ref="I168" r:id="rId110" xr:uid="{FB94721C-B471-4FFC-94E3-E5FFB4C70F01}"/>
+    <hyperlink ref="I159" r:id="rId111" xr:uid="{150CB30D-CB02-4AC9-9051-241A21E88CDC}"/>
+    <hyperlink ref="I138" r:id="rId112" xr:uid="{A6B84085-FB9A-498B-AE4F-74A0C62F54A1}"/>
+    <hyperlink ref="I141" r:id="rId113" xr:uid="{53BEF60D-BF1D-48BC-934B-D23ED97F1DF2}"/>
+    <hyperlink ref="I149" r:id="rId114" xr:uid="{01A532C8-7B79-4FD1-8815-4CFFBAA5FC3A}"/>
+    <hyperlink ref="I123" r:id="rId115" xr:uid="{8F603BDF-34E8-4EB7-B9FA-CA2AEAEF7E18}"/>
     <hyperlink ref="I9" r:id="rId116" xr:uid="{ABE98320-87C3-47AE-B82D-7278F984CC97}"/>
-    <hyperlink ref="I75" r:id="rId117" xr:uid="{7BF0809C-A047-4C14-9F02-722E0B6D702E}"/>
-    <hyperlink ref="I70" r:id="rId118" xr:uid="{A4B01966-B286-4AE7-8C6F-4CD6D053EBB2}"/>
-    <hyperlink ref="I175" r:id="rId119" xr:uid="{EBA727FD-8712-472C-A9DD-A4D394110120}"/>
-    <hyperlink ref="I174" r:id="rId120" xr:uid="{FFAE2B9D-B30D-4BFF-9A8C-8B6F5C00B147}"/>
-    <hyperlink ref="I139" r:id="rId121" xr:uid="{3340B124-7853-47B2-B955-5239901249FE}"/>
-    <hyperlink ref="I114" r:id="rId122" xr:uid="{45968C5C-6D9E-4925-896D-B0493897A25A}"/>
-    <hyperlink ref="I153" r:id="rId123" xr:uid="{857BFC10-B291-4037-82A8-2E2E60E1B1A3}"/>
-    <hyperlink ref="I130" r:id="rId124" xr:uid="{55BFAAD0-936D-4479-AE6F-429EB09B7E59}"/>
-    <hyperlink ref="I154" r:id="rId125" xr:uid="{C864CA34-4B90-4610-935B-584C80DE1894}"/>
-    <hyperlink ref="I155" r:id="rId126" xr:uid="{8EA40152-FC08-4269-8C04-67550D09DD6E}"/>
-    <hyperlink ref="I159" r:id="rId127" xr:uid="{F1BD879D-F4B0-4597-A8E3-E63FD05C6CD0}"/>
-    <hyperlink ref="I124" r:id="rId128" xr:uid="{3530E826-CCF2-4000-BC03-89225BF84689}"/>
-    <hyperlink ref="I160" r:id="rId129" xr:uid="{1D7D92BC-A83B-4B2D-BDC1-AFF8410C9AC2}"/>
-    <hyperlink ref="I176" r:id="rId130" xr:uid="{5F8B4852-646F-4D60-B679-A66FEE5DF003}"/>
-    <hyperlink ref="I137" r:id="rId131" xr:uid="{839C55D4-ECBC-4C90-812C-6B98FE66D026}"/>
-    <hyperlink ref="I149" r:id="rId132" xr:uid="{E872F313-7522-4471-9114-A21C61F3BCF5}"/>
-    <hyperlink ref="I102" r:id="rId133" xr:uid="{E64F7ECF-A4AB-4D69-9264-4167205E0C77}"/>
-    <hyperlink ref="I152" r:id="rId134" xr:uid="{24402103-542E-4590-981D-E088E0944D7F}"/>
-    <hyperlink ref="I140" r:id="rId135" xr:uid="{19B3EDAB-0402-4C2E-ABD4-2E832B044065}"/>
-    <hyperlink ref="I131" r:id="rId136" xr:uid="{CB4A6AA9-63C8-4594-B830-BCF7369727E7}"/>
-    <hyperlink ref="I132" r:id="rId137" xr:uid="{9DE9D6D9-BCDE-4F08-9CBF-68CC3C5B3588}"/>
-    <hyperlink ref="I172" r:id="rId138" xr:uid="{4214FFFB-F38B-4EE4-9F10-1A0BA36E6A85}"/>
-    <hyperlink ref="I120" r:id="rId139" xr:uid="{512D94C9-8DD4-409D-8760-7CA839C39C54}"/>
-    <hyperlink ref="I143" r:id="rId140" xr:uid="{D334BC22-90E9-4D92-9876-CC1DA710007D}"/>
-    <hyperlink ref="I84" r:id="rId141" xr:uid="{94D204A9-5E4D-4A95-A599-800FEDDB797D}"/>
-    <hyperlink ref="I97" r:id="rId142" xr:uid="{19EB9DC2-EA04-4BBD-BF61-2157A76B0465}"/>
-    <hyperlink ref="I83" r:id="rId143" xr:uid="{B2602FC3-562B-4450-AE71-6C74BD000164}"/>
-    <hyperlink ref="I79" r:id="rId144" xr:uid="{B8E55B8D-E70B-49AA-96CE-9DA08787446A}"/>
-    <hyperlink ref="I98" r:id="rId145" xr:uid="{16806685-6D18-4664-A618-1F5B0A1E607E}"/>
-    <hyperlink ref="I64" r:id="rId146" xr:uid="{A5C3EADF-75C6-4A88-9BA3-BEC8BC5D39BC}"/>
-    <hyperlink ref="I68" r:id="rId147" xr:uid="{FD1532C9-0430-431C-9901-299067B36403}"/>
-    <hyperlink ref="I93" r:id="rId148" xr:uid="{CBEF629E-4E10-4A86-A9E6-CB082B86F670}"/>
-    <hyperlink ref="I69" r:id="rId149" xr:uid="{B13A0C04-116F-484D-B425-212BECFEF42E}"/>
-    <hyperlink ref="I92" r:id="rId150" xr:uid="{D60F4CA6-D17C-4FD0-BC2A-4F25AD19071E}"/>
-    <hyperlink ref="I62" r:id="rId151" xr:uid="{61E0C2F6-6914-4712-A486-F3962A11C41F}"/>
-    <hyperlink ref="I73" r:id="rId152" xr:uid="{D04A3AAE-3351-46C8-AC0E-9E5B45F98BE2}"/>
-    <hyperlink ref="I58" r:id="rId153" xr:uid="{CC5C0DA7-B351-4340-B0F0-D8F19523E615}"/>
-    <hyperlink ref="I91" r:id="rId154" xr:uid="{05468504-6738-41B8-8AF1-6DAA72A25D9D}"/>
-    <hyperlink ref="I104" r:id="rId155" xr:uid="{A96359A5-6DFF-4CDE-9DEB-3266734E97C7}"/>
-    <hyperlink ref="I77" r:id="rId156" xr:uid="{30BA92C9-344D-4BEF-BCAA-A9F4623D85CA}"/>
-    <hyperlink ref="I109" r:id="rId157" xr:uid="{7F3FC5DE-4FEC-4D00-BF8C-78FEDEE6B304}"/>
-    <hyperlink ref="I76" r:id="rId158" xr:uid="{6E70B454-8E64-41C3-A126-B2FC1E33FE3B}"/>
-    <hyperlink ref="I82" r:id="rId159" xr:uid="{39F407AC-C5F0-4B9A-80FC-CCFF41ADB6A2}"/>
-    <hyperlink ref="I96" r:id="rId160" xr:uid="{12857E91-BA27-4FC0-B258-741B6ADBD89F}"/>
-    <hyperlink ref="I103" r:id="rId161" xr:uid="{1E898AF7-1279-446A-AC90-0E57338F2F75}"/>
-    <hyperlink ref="I90" r:id="rId162" xr:uid="{C804C3D1-BD84-4033-ACE8-89AB44334955}"/>
-    <hyperlink ref="I105" r:id="rId163" xr:uid="{5AC377AD-6B01-4C2E-96BD-7C03C6C4DA8D}"/>
-    <hyperlink ref="I61" r:id="rId164" xr:uid="{CAAAC944-BB6D-437A-97BC-DF247A41C992}"/>
+    <hyperlink ref="I135" r:id="rId117" xr:uid="{7BF0809C-A047-4C14-9F02-722E0B6D702E}"/>
+    <hyperlink ref="I130" r:id="rId118" xr:uid="{A4B01966-B286-4AE7-8C6F-4CD6D053EBB2}"/>
+    <hyperlink ref="I115" r:id="rId119" xr:uid="{EBA727FD-8712-472C-A9DD-A4D394110120}"/>
+    <hyperlink ref="I114" r:id="rId120" xr:uid="{FFAE2B9D-B30D-4BFF-9A8C-8B6F5C00B147}"/>
+    <hyperlink ref="I79" r:id="rId121" xr:uid="{3340B124-7853-47B2-B955-5239901249FE}"/>
+    <hyperlink ref="I174" r:id="rId122" xr:uid="{45968C5C-6D9E-4925-896D-B0493897A25A}"/>
+    <hyperlink ref="I93" r:id="rId123" xr:uid="{857BFC10-B291-4037-82A8-2E2E60E1B1A3}"/>
+    <hyperlink ref="I70" r:id="rId124" xr:uid="{55BFAAD0-936D-4479-AE6F-429EB09B7E59}"/>
+    <hyperlink ref="I94" r:id="rId125" xr:uid="{C864CA34-4B90-4610-935B-584C80DE1894}"/>
+    <hyperlink ref="I95" r:id="rId126" xr:uid="{8EA40152-FC08-4269-8C04-67550D09DD6E}"/>
+    <hyperlink ref="I99" r:id="rId127" xr:uid="{F1BD879D-F4B0-4597-A8E3-E63FD05C6CD0}"/>
+    <hyperlink ref="I64" r:id="rId128" xr:uid="{3530E826-CCF2-4000-BC03-89225BF84689}"/>
+    <hyperlink ref="I100" r:id="rId129" xr:uid="{1D7D92BC-A83B-4B2D-BDC1-AFF8410C9AC2}"/>
+    <hyperlink ref="I116" r:id="rId130" xr:uid="{5F8B4852-646F-4D60-B679-A66FEE5DF003}"/>
+    <hyperlink ref="I77" r:id="rId131" xr:uid="{839C55D4-ECBC-4C90-812C-6B98FE66D026}"/>
+    <hyperlink ref="I89" r:id="rId132" xr:uid="{E872F313-7522-4471-9114-A21C61F3BCF5}"/>
+    <hyperlink ref="I162" r:id="rId133" xr:uid="{E64F7ECF-A4AB-4D69-9264-4167205E0C77}"/>
+    <hyperlink ref="I92" r:id="rId134" xr:uid="{24402103-542E-4590-981D-E088E0944D7F}"/>
+    <hyperlink ref="I80" r:id="rId135" xr:uid="{19B3EDAB-0402-4C2E-ABD4-2E832B044065}"/>
+    <hyperlink ref="I71" r:id="rId136" xr:uid="{CB4A6AA9-63C8-4594-B830-BCF7369727E7}"/>
+    <hyperlink ref="I72" r:id="rId137" xr:uid="{9DE9D6D9-BCDE-4F08-9CBF-68CC3C5B3588}"/>
+    <hyperlink ref="I112" r:id="rId138" xr:uid="{4214FFFB-F38B-4EE4-9F10-1A0BA36E6A85}"/>
+    <hyperlink ref="I60" r:id="rId139" xr:uid="{512D94C9-8DD4-409D-8760-7CA839C39C54}"/>
+    <hyperlink ref="I83" r:id="rId140" xr:uid="{D334BC22-90E9-4D92-9876-CC1DA710007D}"/>
+    <hyperlink ref="I144" r:id="rId141" xr:uid="{94D204A9-5E4D-4A95-A599-800FEDDB797D}"/>
+    <hyperlink ref="I157" r:id="rId142" xr:uid="{19EB9DC2-EA04-4BBD-BF61-2157A76B0465}"/>
+    <hyperlink ref="I143" r:id="rId143" xr:uid="{B2602FC3-562B-4450-AE71-6C74BD000164}"/>
+    <hyperlink ref="I139" r:id="rId144" xr:uid="{B8E55B8D-E70B-49AA-96CE-9DA08787446A}"/>
+    <hyperlink ref="I158" r:id="rId145" xr:uid="{16806685-6D18-4664-A618-1F5B0A1E607E}"/>
+    <hyperlink ref="I124" r:id="rId146" xr:uid="{A5C3EADF-75C6-4A88-9BA3-BEC8BC5D39BC}"/>
+    <hyperlink ref="I128" r:id="rId147" xr:uid="{FD1532C9-0430-431C-9901-299067B36403}"/>
+    <hyperlink ref="I153" r:id="rId148" xr:uid="{CBEF629E-4E10-4A86-A9E6-CB082B86F670}"/>
+    <hyperlink ref="I129" r:id="rId149" xr:uid="{B13A0C04-116F-484D-B425-212BECFEF42E}"/>
+    <hyperlink ref="I152" r:id="rId150" xr:uid="{D60F4CA6-D17C-4FD0-BC2A-4F25AD19071E}"/>
+    <hyperlink ref="I122" r:id="rId151" xr:uid="{61E0C2F6-6914-4712-A486-F3962A11C41F}"/>
+    <hyperlink ref="I133" r:id="rId152" xr:uid="{D04A3AAE-3351-46C8-AC0E-9E5B45F98BE2}"/>
+    <hyperlink ref="I118" r:id="rId153" xr:uid="{CC5C0DA7-B351-4340-B0F0-D8F19523E615}"/>
+    <hyperlink ref="I151" r:id="rId154" xr:uid="{05468504-6738-41B8-8AF1-6DAA72A25D9D}"/>
+    <hyperlink ref="I164" r:id="rId155" xr:uid="{A96359A5-6DFF-4CDE-9DEB-3266734E97C7}"/>
+    <hyperlink ref="I137" r:id="rId156" xr:uid="{30BA92C9-344D-4BEF-BCAA-A9F4623D85CA}"/>
+    <hyperlink ref="I169" r:id="rId157" xr:uid="{7F3FC5DE-4FEC-4D00-BF8C-78FEDEE6B304}"/>
+    <hyperlink ref="I136" r:id="rId158" xr:uid="{6E70B454-8E64-41C3-A126-B2FC1E33FE3B}"/>
+    <hyperlink ref="I142" r:id="rId159" xr:uid="{39F407AC-C5F0-4B9A-80FC-CCFF41ADB6A2}"/>
+    <hyperlink ref="I156" r:id="rId160" xr:uid="{12857E91-BA27-4FC0-B258-741B6ADBD89F}"/>
+    <hyperlink ref="I163" r:id="rId161" xr:uid="{1E898AF7-1279-446A-AC90-0E57338F2F75}"/>
+    <hyperlink ref="I150" r:id="rId162" xr:uid="{C804C3D1-BD84-4033-ACE8-89AB44334955}"/>
+    <hyperlink ref="I165" r:id="rId163" xr:uid="{5AC377AD-6B01-4C2E-96BD-7C03C6C4DA8D}"/>
+    <hyperlink ref="I121" r:id="rId164" xr:uid="{CAAAC944-BB6D-437A-97BC-DF247A41C992}"/>
     <hyperlink ref="I2" r:id="rId165" xr:uid="{27158B26-0953-4A76-8B15-FCA78DBB52DB}"/>
-    <hyperlink ref="I100" r:id="rId166" xr:uid="{34AD736F-32FD-461C-AF0D-C0B8822C1F79}"/>
-    <hyperlink ref="I86" r:id="rId167" xr:uid="{5CBC833A-065B-4956-825D-5C9E4DF073F2}"/>
-    <hyperlink ref="I110" r:id="rId168" xr:uid="{9C63AC25-E60D-4EC3-B637-D741A00D2042}"/>
-    <hyperlink ref="I101" r:id="rId169" xr:uid="{B7C89EB2-C0E0-4896-862A-A3CE1D0ADB4F}"/>
-    <hyperlink ref="I95" r:id="rId170" xr:uid="{EAC2B9B4-49CA-49BA-9AD1-1E5E31DDDE63}"/>
-    <hyperlink ref="I173" r:id="rId171" xr:uid="{9E382C51-B975-42DA-B726-D65A7BA7E43E}"/>
-    <hyperlink ref="I125" r:id="rId172" xr:uid="{F500A640-9D37-4CD5-A47D-330EA5A80C37}"/>
+    <hyperlink ref="I160" r:id="rId166" xr:uid="{34AD736F-32FD-461C-AF0D-C0B8822C1F79}"/>
+    <hyperlink ref="I146" r:id="rId167" xr:uid="{5CBC833A-065B-4956-825D-5C9E4DF073F2}"/>
+    <hyperlink ref="I170" r:id="rId168" xr:uid="{9C63AC25-E60D-4EC3-B637-D741A00D2042}"/>
+    <hyperlink ref="I161" r:id="rId169" xr:uid="{B7C89EB2-C0E0-4896-862A-A3CE1D0ADB4F}"/>
+    <hyperlink ref="I155" r:id="rId170" xr:uid="{EAC2B9B4-49CA-49BA-9AD1-1E5E31DDDE63}"/>
+    <hyperlink ref="I113" r:id="rId171" xr:uid="{9E382C51-B975-42DA-B726-D65A7BA7E43E}"/>
+    <hyperlink ref="I65" r:id="rId172" xr:uid="{F500A640-9D37-4CD5-A47D-330EA5A80C37}"/>
     <hyperlink ref="I202" r:id="rId173" xr:uid="{42EEDCF1-F980-4D63-82CF-4DC729038221}"/>
     <hyperlink ref="I196" r:id="rId174" xr:uid="{E099B2D0-E1B1-408A-81E6-962F50045CDA}"/>
     <hyperlink ref="I204" r:id="rId175" xr:uid="{C5D193ED-4696-4F83-8343-8032BB681087}"/>
@@ -7714,17 +7714,17 @@
     <hyperlink ref="I218" r:id="rId197" xr:uid="{A10580CC-6AE9-45DA-BDF1-A6ED199E7AB7}"/>
     <hyperlink ref="I230" r:id="rId198" xr:uid="{73AD760F-094A-49D1-8088-C0545817A477}"/>
     <hyperlink ref="I235" r:id="rId199" xr:uid="{C234AC10-6324-4DD6-A058-75F1F9CA6F12}"/>
-    <hyperlink ref="I67" r:id="rId200" xr:uid="{F5C97B0E-A756-4DE1-841D-6B1CB25F25AB}"/>
+    <hyperlink ref="I127" r:id="rId200" xr:uid="{F5C97B0E-A756-4DE1-841D-6B1CB25F25AB}"/>
     <hyperlink ref="I210" r:id="rId201" xr:uid="{3A611A5A-52E7-4B2D-8E8B-91A2B3A2EFE6}"/>
     <hyperlink ref="I221" r:id="rId202" xr:uid="{9B88E7A4-7AB9-4609-902B-447AA256A22E}"/>
     <hyperlink ref="I237" r:id="rId203" xr:uid="{16B5784E-F92A-4463-8CA6-D1A4C1500DDC}"/>
-    <hyperlink ref="I66" r:id="rId204" xr:uid="{A11B1E4A-41EF-4617-8845-21061174EC6B}"/>
-    <hyperlink ref="I85" r:id="rId205" xr:uid="{D872B77B-223B-4BF0-BD8C-DAAC2B0EDC99}"/>
+    <hyperlink ref="I126" r:id="rId204" xr:uid="{A11B1E4A-41EF-4617-8845-21061174EC6B}"/>
+    <hyperlink ref="I145" r:id="rId205" xr:uid="{D872B77B-223B-4BF0-BD8C-DAAC2B0EDC99}"/>
     <hyperlink ref="I225" r:id="rId206" xr:uid="{C93D61B2-FB23-44D0-AE82-86CFCBE87E31}"/>
     <hyperlink ref="I209" r:id="rId207" xr:uid="{D86B3813-9911-45F9-8FE1-97CB1D382921}"/>
     <hyperlink ref="I206" r:id="rId208" xr:uid="{83F85360-7B3C-408F-8FC3-DC7ED9BEF52A}"/>
     <hyperlink ref="I211" r:id="rId209" xr:uid="{81A402A6-17B5-4660-A5FA-8891051AFD8A}"/>
-    <hyperlink ref="I106" r:id="rId210" xr:uid="{76B6A52C-076E-4845-B26C-F7BAA6C30430}"/>
+    <hyperlink ref="I166" r:id="rId210" xr:uid="{76B6A52C-076E-4845-B26C-F7BAA6C30430}"/>
     <hyperlink ref="I222" r:id="rId211" xr:uid="{9A1A11F7-AD8B-47F0-87A3-8CACA6F2F4C7}"/>
     <hyperlink ref="I226" r:id="rId212" xr:uid="{064F1840-F71C-47C2-9F8A-E9CC6E203674}"/>
     <hyperlink ref="I224" r:id="rId213" xr:uid="{265E5CC6-C099-4295-AF9E-712181DBF85D}"/>
@@ -7732,7 +7732,7 @@
     <hyperlink ref="I213" r:id="rId215" xr:uid="{12901D47-8902-41FB-BE93-FB91AA7CE8E5}"/>
     <hyperlink ref="I232" r:id="rId216" xr:uid="{C139B65F-A76A-492E-A650-5F3ACF0EA096}"/>
     <hyperlink ref="I219" r:id="rId217" xr:uid="{5BFBC30B-5F84-47F5-87A8-924092803241}"/>
-    <hyperlink ref="I71" r:id="rId218" xr:uid="{C2FEEE03-74B0-4453-9355-675F9D619B6D}"/>
+    <hyperlink ref="I131" r:id="rId218" xr:uid="{C2FEEE03-74B0-4453-9355-675F9D619B6D}"/>
     <hyperlink ref="I214" r:id="rId219" xr:uid="{D9A906FF-B66D-412D-8BE7-45B3B2CF68CB}"/>
     <hyperlink ref="I223" r:id="rId220" xr:uid="{52768E1D-0D83-4158-9941-D3FE248FCC03}"/>
     <hyperlink ref="I231" r:id="rId221" xr:uid="{90E84A57-1F82-4F32-9D1C-7865BC6BE4A4}"/>

--- a/AKC.xlsx
+++ b/AKC.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="156" documentId="11_E84A2F77117A4CCFEB3B98154B1BF678960CE3E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57F11C48-472A-4F29-A479-8CD368143536}"/>
+  <xr:revisionPtr revIDLastSave="161" documentId="11_E84A2F77117A4CCFEB3B98154B1BF678960CE3E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C69257DB-A731-4328-83A4-BF5E3CACBA2A}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3979,7 +3979,7 @@
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>238</v>
@@ -3998,7 +3998,7 @@
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
       <c r="D113" s="2" t="s">
-        <v>133</v>
+        <v>10</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>240</v>
@@ -4017,7 +4017,7 @@
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
       <c r="D114" s="2" t="s">
-        <v>133</v>
+        <v>10</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>242</v>
@@ -4036,7 +4036,7 @@
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
       <c r="D115" s="2" t="s">
-        <v>133</v>
+        <v>10</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>244</v>
@@ -4055,7 +4055,7 @@
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
       <c r="D116" s="2" t="s">
-        <v>133</v>
+        <v>10</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>246</v>

--- a/AKC.xlsx
+++ b/AKC.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="161" documentId="11_E84A2F77117A4CCFEB3B98154B1BF678960CE3E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C69257DB-A731-4328-83A4-BF5E3CACBA2A}"/>
+  <xr:revisionPtr revIDLastSave="156" documentId="11_E84A2F77117A4CCFEB3B98154B1BF678960CE3E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57F11C48-472A-4F29-A479-8CD368143536}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3979,7 +3979,7 @@
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2" t="s">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>238</v>
@@ -3998,7 +3998,7 @@
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
       <c r="D113" s="2" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>240</v>
@@ -4017,7 +4017,7 @@
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
       <c r="D114" s="2" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>242</v>
@@ -4036,7 +4036,7 @@
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
       <c r="D115" s="2" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>244</v>
@@ -4055,7 +4055,7 @@
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
       <c r="D116" s="2" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>246</v>

--- a/AKC.xlsx
+++ b/AKC.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="161" documentId="11_E84A2F77117A4CCFEB3B98154B1BF678960CE3E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C69257DB-A731-4328-83A4-BF5E3CACBA2A}"/>
+  <xr:revisionPtr revIDLastSave="163" documentId="11_E84A2F77117A4CCFEB3B98154B1BF678960CE3E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3521466-AC9F-458C-86FA-54C1F6B59615}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1158,7 +1158,7 @@
     <t>https://youtube.com/shorts/I9CPmi6pxyQ</t>
   </si>
   <si>
-    <t>Orientación</t>
+    <t>Orientacion</t>
   </si>
   <si>
     <t>Orientación aérea</t>

--- a/AKC.xlsx
+++ b/AKC.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="163" documentId="11_E84A2F77117A4CCFEB3B98154B1BF678960CE3E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3521466-AC9F-458C-86FA-54C1F6B59615}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="11_E84A2F77117A4CCFEB3B98154B1BF678960CE3E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2A15B9E-ECC5-487D-BE7D-9C4A353E67F1}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="486">
   <si>
     <t>Tipo</t>
   </si>
@@ -1156,6 +1156,15 @@
   </si>
   <si>
     <t>https://youtube.com/shorts/I9CPmi6pxyQ</t>
+  </si>
+  <si>
+    <t>Orientación</t>
+  </si>
+  <si>
+    <t>prueba</t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
   <si>
     <t>Orientacion</t>
@@ -1838,7 +1847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K239"/>
+  <dimension ref="A1:K241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -6205,437 +6214,409 @@
       <c r="D188" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="E188" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
-      <c r="I188" s="3" t="s">
-        <v>378</v>
-      </c>
+      <c r="I188" s="3"/>
     </row>
     <row r="189" spans="1:9">
       <c r="A189" s="2" t="s">
         <v>375</v>
       </c>
       <c r="B189" s="2"/>
-      <c r="C189" s="2">
-        <v>1</v>
-      </c>
+      <c r="C189" s="2"/>
       <c r="D189" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
-      <c r="I189" s="3" t="s">
-        <v>380</v>
-      </c>
+      <c r="I189" s="3"/>
     </row>
     <row r="190" spans="1:9">
       <c r="A190" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B190" s="2"/>
       <c r="C190" s="2">
         <v>1</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
       <c r="I190" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="191" spans="1:9">
       <c r="A191" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B191" s="2"/>
       <c r="C191" s="2">
         <v>1</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
       <c r="I191" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="192" spans="1:9">
       <c r="A192" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B192" s="2"/>
       <c r="C192" s="2">
         <v>1</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
       <c r="I192" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="193" spans="1:9">
       <c r="A193" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B193" s="2"/>
       <c r="C193" s="2">
         <v>1</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
       <c r="I193" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="194" spans="1:9">
       <c r="A194" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B194" s="2"/>
       <c r="C194" s="2">
         <v>1</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
       <c r="I194" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="195" spans="1:9">
       <c r="A195" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B195" s="2"/>
       <c r="C195" s="2">
         <v>1</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
       <c r="I195" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="196" spans="1:9">
       <c r="A196" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B196" s="2"/>
       <c r="C196" s="2">
         <v>1</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
       <c r="I196" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="197" spans="1:9">
       <c r="A197" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B197" s="2"/>
       <c r="C197" s="2">
         <v>1</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
       <c r="I197" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="198" spans="1:9">
       <c r="A198" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B198" s="2"/>
       <c r="C198" s="2">
         <v>1</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
       <c r="I198" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="199" spans="1:9">
       <c r="A199" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B199" s="2"/>
       <c r="C199" s="2">
         <v>1</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
       <c r="I199" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="200" spans="1:9">
       <c r="A200" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" s="2">
         <v>1</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
       <c r="I200" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="201" spans="1:9">
       <c r="A201" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B201" s="2"/>
       <c r="C201" s="2">
         <v>1</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
       <c r="I201" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="202" spans="1:9">
       <c r="A202" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B202" s="2"/>
       <c r="C202" s="2">
         <v>1</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
       <c r="I202" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="203" spans="1:9">
       <c r="A203" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B203" s="2"/>
       <c r="C203" s="2">
         <v>1</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
       <c r="I203" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="204" spans="1:9">
       <c r="A204" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B204" s="2"/>
       <c r="C204" s="2">
         <v>1</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F204" s="2"/>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
       <c r="I204" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="205" spans="1:9">
       <c r="A205" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B205" s="2"/>
       <c r="C205" s="2">
         <v>1</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F205" s="2"/>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
       <c r="I205" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="206" spans="1:9">
       <c r="A206" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B206" s="2"/>
+      <c r="C206" s="2">
+        <v>1</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="F206" s="2"/>
+      <c r="G206" s="2"/>
+      <c r="H206" s="2"/>
+      <c r="I206" s="3" t="s">
         <v>413</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="C206" s="2">
-        <v>1</v>
-      </c>
-      <c r="D206" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F206" s="2">
-        <v>1</v>
-      </c>
-      <c r="G206" s="2">
-        <v>12</v>
-      </c>
-      <c r="H206" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="I206" s="3" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="207" spans="1:9">
       <c r="A207" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="B207" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B207" s="2"/>
+      <c r="C207" s="2">
+        <v>1</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E207" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C207" s="2">
-        <v>1</v>
-      </c>
-      <c r="D207" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="F207" s="2">
-        <v>1</v>
-      </c>
-      <c r="G207" s="2">
-        <v>12</v>
-      </c>
-      <c r="H207" s="2" t="s">
-        <v>251</v>
-      </c>
+      <c r="F207" s="2"/>
+      <c r="G207" s="2"/>
+      <c r="H207" s="2"/>
       <c r="I207" s="3" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="208" spans="1:9">
       <c r="A208" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C208" s="2">
         <v>1</v>
@@ -6644,7 +6625,7 @@
         <v>133</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F208" s="2">
         <v>1</v>
@@ -6656,15 +6637,15 @@
         <v>251</v>
       </c>
       <c r="I208" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="209" spans="1:9">
       <c r="A209" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C209" s="2">
         <v>1</v>
@@ -6673,7 +6654,7 @@
         <v>133</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F209" s="2">
         <v>1</v>
@@ -6685,15 +6666,15 @@
         <v>251</v>
       </c>
       <c r="I209" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="210" spans="1:9">
       <c r="A210" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C210" s="2">
         <v>1</v>
@@ -6702,7 +6683,7 @@
         <v>133</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F210" s="2">
         <v>1</v>
@@ -6714,15 +6695,15 @@
         <v>251</v>
       </c>
       <c r="I210" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="211" spans="1:9">
       <c r="A211" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C211" s="2">
         <v>1</v>
@@ -6731,7 +6712,7 @@
         <v>133</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F211" s="2">
         <v>1</v>
@@ -6743,15 +6724,15 @@
         <v>251</v>
       </c>
       <c r="I211" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="212" spans="1:9">
       <c r="A212" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C212" s="2">
         <v>1</v>
@@ -6760,7 +6741,7 @@
         <v>133</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F212" s="2">
         <v>1</v>
@@ -6772,15 +6753,15 @@
         <v>251</v>
       </c>
       <c r="I212" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="213" spans="1:9">
       <c r="A213" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C213" s="2">
         <v>1</v>
@@ -6789,7 +6770,7 @@
         <v>133</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F213" s="2">
         <v>1</v>
@@ -6801,15 +6782,15 @@
         <v>251</v>
       </c>
       <c r="I213" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="214" spans="1:9">
       <c r="A214" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C214" s="2">
         <v>1</v>
@@ -6818,7 +6799,7 @@
         <v>133</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F214" s="2">
         <v>1</v>
@@ -6830,15 +6811,15 @@
         <v>251</v>
       </c>
       <c r="I214" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="215" spans="1:9">
       <c r="A215" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C215" s="2">
         <v>1</v>
@@ -6847,7 +6828,7 @@
         <v>133</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F215" s="2">
         <v>1</v>
@@ -6859,24 +6840,24 @@
         <v>251</v>
       </c>
       <c r="I215" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="216" spans="1:9">
       <c r="A216" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C216" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>133</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F216" s="2">
         <v>1</v>
@@ -6884,26 +6865,28 @@
       <c r="G216" s="2">
         <v>12</v>
       </c>
-      <c r="H216" s="2"/>
+      <c r="H216" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I216" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="217" spans="1:9">
       <c r="A217" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C217" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>133</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F217" s="2">
         <v>1</v>
@@ -6911,17 +6894,19 @@
       <c r="G217" s="2">
         <v>12</v>
       </c>
-      <c r="H217" s="2"/>
+      <c r="H217" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="I217" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="218" spans="1:9">
       <c r="A218" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C218" s="2">
         <v>2</v>
@@ -6930,7 +6915,7 @@
         <v>133</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F218" s="2">
         <v>1</v>
@@ -6940,15 +6925,15 @@
       </c>
       <c r="H218" s="2"/>
       <c r="I218" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="219" spans="1:9">
       <c r="A219" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C219" s="2">
         <v>2</v>
@@ -6957,7 +6942,7 @@
         <v>133</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F219" s="2">
         <v>1</v>
@@ -6967,15 +6952,15 @@
       </c>
       <c r="H219" s="2"/>
       <c r="I219" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="220" spans="1:9">
       <c r="A220" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C220" s="2">
         <v>2</v>
@@ -6984,7 +6969,7 @@
         <v>133</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F220" s="2">
         <v>1</v>
@@ -6994,15 +6979,15 @@
       </c>
       <c r="H220" s="2"/>
       <c r="I220" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="221" spans="1:9">
       <c r="A221" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C221" s="2">
         <v>2</v>
@@ -7011,7 +6996,7 @@
         <v>133</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F221" s="2">
         <v>1</v>
@@ -7021,15 +7006,15 @@
       </c>
       <c r="H221" s="2"/>
       <c r="I221" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="222" spans="1:9">
       <c r="A222" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C222" s="2">
         <v>2</v>
@@ -7038,7 +7023,7 @@
         <v>133</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F222" s="2">
         <v>1</v>
@@ -7048,15 +7033,15 @@
       </c>
       <c r="H222" s="2"/>
       <c r="I222" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="223" spans="1:9">
       <c r="A223" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C223" s="2">
         <v>2</v>
@@ -7065,7 +7050,7 @@
         <v>133</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F223" s="2">
         <v>1</v>
@@ -7075,24 +7060,24 @@
       </c>
       <c r="H223" s="2"/>
       <c r="I223" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="224" spans="1:9">
       <c r="A224" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C224" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>133</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F224" s="2">
         <v>1</v>
@@ -7102,24 +7087,24 @@
       </c>
       <c r="H224" s="2"/>
       <c r="I224" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="225" spans="1:9">
       <c r="A225" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C225" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>133</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F225" s="2">
         <v>1</v>
@@ -7129,15 +7114,15 @@
       </c>
       <c r="H225" s="2"/>
       <c r="I225" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="226" spans="1:9">
       <c r="A226" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C226" s="2">
         <v>3</v>
@@ -7146,7 +7131,7 @@
         <v>133</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F226" s="2">
         <v>1</v>
@@ -7156,15 +7141,15 @@
       </c>
       <c r="H226" s="2"/>
       <c r="I226" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="227" spans="1:9">
       <c r="A227" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C227" s="2">
         <v>3</v>
@@ -7173,7 +7158,7 @@
         <v>133</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F227" s="2">
         <v>1</v>
@@ -7183,15 +7168,15 @@
       </c>
       <c r="H227" s="2"/>
       <c r="I227" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="228" spans="1:9">
       <c r="A228" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C228" s="2">
         <v>3</v>
@@ -7200,7 +7185,7 @@
         <v>133</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F228" s="2">
         <v>1</v>
@@ -7210,15 +7195,15 @@
       </c>
       <c r="H228" s="2"/>
       <c r="I228" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="229" spans="1:9">
       <c r="A229" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C229" s="2">
         <v>3</v>
@@ -7227,7 +7212,7 @@
         <v>133</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F229" s="2">
         <v>1</v>
@@ -7237,15 +7222,15 @@
       </c>
       <c r="H229" s="2"/>
       <c r="I229" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="230" spans="1:9">
       <c r="A230" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C230" s="2">
         <v>3</v>
@@ -7254,7 +7239,7 @@
         <v>133</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F230" s="2">
         <v>1</v>
@@ -7264,15 +7249,15 @@
       </c>
       <c r="H230" s="2"/>
       <c r="I230" s="3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="231" spans="1:9">
       <c r="A231" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C231" s="2">
         <v>3</v>
@@ -7281,7 +7266,7 @@
         <v>133</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F231" s="2">
         <v>1</v>
@@ -7291,24 +7276,24 @@
       </c>
       <c r="H231" s="2"/>
       <c r="I231" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="232" spans="1:9">
       <c r="A232" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C232" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>133</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F232" s="2">
         <v>1</v>
@@ -7318,24 +7303,24 @@
       </c>
       <c r="H232" s="2"/>
       <c r="I232" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="233" spans="1:9">
       <c r="A233" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C233" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>133</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F233" s="2">
         <v>1</v>
@@ -7345,15 +7330,15 @@
       </c>
       <c r="H233" s="2"/>
       <c r="I233" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="234" spans="1:9">
       <c r="A234" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C234" s="2">
         <v>4</v>
@@ -7362,7 +7347,7 @@
         <v>133</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F234" s="2">
         <v>1</v>
@@ -7372,15 +7357,15 @@
       </c>
       <c r="H234" s="2"/>
       <c r="I234" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="235" spans="1:9">
       <c r="A235" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C235" s="2">
         <v>4</v>
@@ -7389,7 +7374,7 @@
         <v>133</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F235" s="2">
         <v>1</v>
@@ -7399,15 +7384,15 @@
       </c>
       <c r="H235" s="2"/>
       <c r="I235" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="236" spans="1:9">
       <c r="A236" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C236" s="2">
         <v>4</v>
@@ -7416,7 +7401,7 @@
         <v>133</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F236" s="2">
         <v>1</v>
@@ -7426,15 +7411,15 @@
       </c>
       <c r="H236" s="2"/>
       <c r="I236" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="237" spans="1:9">
       <c r="A237" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C237" s="2">
         <v>4</v>
@@ -7443,7 +7428,7 @@
         <v>133</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F237" s="2">
         <v>1</v>
@@ -7453,15 +7438,15 @@
       </c>
       <c r="H237" s="2"/>
       <c r="I237" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="238" spans="1:9">
       <c r="A238" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C238" s="2">
         <v>4</v>
@@ -7470,7 +7455,7 @@
         <v>133</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F238" s="2">
         <v>1</v>
@@ -7480,15 +7465,15 @@
       </c>
       <c r="H238" s="2"/>
       <c r="I238" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="239" spans="1:9">
       <c r="A239" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C239" s="2">
         <v>4</v>
@@ -7497,7 +7482,7 @@
         <v>133</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F239" s="2">
         <v>1</v>
@@ -7507,16 +7492,70 @@
       </c>
       <c r="H239" s="2"/>
       <c r="I239" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9">
+      <c r="A240" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C240" s="2">
+        <v>4</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E240" s="1" t="s">
         <v>482</v>
       </c>
+      <c r="F240" s="2">
+        <v>1</v>
+      </c>
+      <c r="G240" s="2">
+        <v>12</v>
+      </c>
+      <c r="H240" s="2"/>
+      <c r="I240" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9">
+      <c r="A241" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C241" s="2">
+        <v>4</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="F241" s="2">
+        <v>1</v>
+      </c>
+      <c r="G241" s="2">
+        <v>12</v>
+      </c>
+      <c r="H241" s="2"/>
+      <c r="I241" s="3" t="s">
+        <v>485</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I239">
-    <sortCondition ref="A2:A239"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I241">
+    <sortCondition ref="A2:A241"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="I220" r:id="rId1" xr:uid="{5FEEF02D-1341-4501-88A4-821F6FD7EF17}"/>
-    <hyperlink ref="I212" r:id="rId2" xr:uid="{5A3DDB27-6AB2-4F01-A380-E2B2770C763C}"/>
+    <hyperlink ref="I222" r:id="rId1" xr:uid="{5FEEF02D-1341-4501-88A4-821F6FD7EF17}"/>
+    <hyperlink ref="I214" r:id="rId2" xr:uid="{5A3DDB27-6AB2-4F01-A380-E2B2770C763C}"/>
     <hyperlink ref="I119" r:id="rId3" xr:uid="{9A2E61CF-14C4-4C29-9CF8-0F94BA115C5A}"/>
     <hyperlink ref="I132" r:id="rId4" xr:uid="{1770959C-0E29-49F6-AB71-FEB65B1CF5D7}"/>
     <hyperlink ref="I34" r:id="rId5" xr:uid="{19BDA2BA-2F24-44AE-B917-BCD6CDF1CFF4}"/>
@@ -7687,61 +7726,61 @@
     <hyperlink ref="I155" r:id="rId170" xr:uid="{EAC2B9B4-49CA-49BA-9AD1-1E5E31DDDE63}"/>
     <hyperlink ref="I113" r:id="rId171" xr:uid="{9E382C51-B975-42DA-B726-D65A7BA7E43E}"/>
     <hyperlink ref="I65" r:id="rId172" xr:uid="{F500A640-9D37-4CD5-A47D-330EA5A80C37}"/>
-    <hyperlink ref="I202" r:id="rId173" xr:uid="{42EEDCF1-F980-4D63-82CF-4DC729038221}"/>
-    <hyperlink ref="I196" r:id="rId174" xr:uid="{E099B2D0-E1B1-408A-81E6-962F50045CDA}"/>
-    <hyperlink ref="I204" r:id="rId175" xr:uid="{C5D193ED-4696-4F83-8343-8032BB681087}"/>
-    <hyperlink ref="I190" r:id="rId176" xr:uid="{28A1299C-CB07-4CBB-A8A8-007396DBE172}"/>
-    <hyperlink ref="I203" r:id="rId177" xr:uid="{A540C09D-E2A9-464E-B6EA-4D2BF932715F}"/>
-    <hyperlink ref="I193" r:id="rId178" xr:uid="{1C532CC2-B9D1-460D-8515-56F1592B3604}"/>
-    <hyperlink ref="I194" r:id="rId179" xr:uid="{F7D956AF-1FAC-4769-9788-F12DBA51D0A1}"/>
-    <hyperlink ref="I195" r:id="rId180" xr:uid="{1E5CBE72-21E0-4942-A5FB-C1798FB51093}"/>
-    <hyperlink ref="I205" r:id="rId181" xr:uid="{E01CA36B-ACE8-42AB-A793-57E82F491D41}"/>
-    <hyperlink ref="I189" r:id="rId182" xr:uid="{0544E67E-AF6D-4F5D-A38D-25CDE152AF1D}"/>
-    <hyperlink ref="I197" r:id="rId183" xr:uid="{B83136C5-9644-4ABB-BEAF-862EB577A44F}"/>
-    <hyperlink ref="I191" r:id="rId184" xr:uid="{DE4C587F-77E5-4309-A006-0343ABBAA9D0}"/>
-    <hyperlink ref="I188" r:id="rId185" xr:uid="{28DEDE56-1057-4101-ADBC-7D4B6DC6649D}"/>
-    <hyperlink ref="I192" r:id="rId186" xr:uid="{40F0F180-7743-464C-9ABD-71168C0718C7}"/>
-    <hyperlink ref="I198" r:id="rId187" xr:uid="{CCD1C6F1-C660-49C3-BFB3-1DB213616385}"/>
-    <hyperlink ref="I200" r:id="rId188" xr:uid="{9380BA53-5C1F-471D-B377-6CC3D652D2EE}"/>
-    <hyperlink ref="I201" r:id="rId189" xr:uid="{38BDDA20-AD35-4AAD-9A61-FEDB55710A94}"/>
-    <hyperlink ref="I199" r:id="rId190" xr:uid="{5C37012F-4705-474B-9B2B-BB1C567310EF}"/>
-    <hyperlink ref="I207" r:id="rId191" xr:uid="{543B344D-C918-44E6-824A-1BAC8D1A3C4A}"/>
-    <hyperlink ref="I217" r:id="rId192" xr:uid="{5649AC79-7139-4508-9C1E-0B3BD28FD5CF}"/>
-    <hyperlink ref="I216" r:id="rId193" xr:uid="{02006E33-3925-433C-80F9-427BACB29AB2}"/>
-    <hyperlink ref="I229" r:id="rId194" xr:uid="{A6387C04-B74B-4755-A998-575207C6D7B8}"/>
-    <hyperlink ref="I234" r:id="rId195" xr:uid="{7D075796-42BC-4E52-B3DC-3AED5CC2B2AF}"/>
-    <hyperlink ref="I208" r:id="rId196" xr:uid="{5BA71668-ECB7-431E-8748-3B21BB00FB80}"/>
-    <hyperlink ref="I218" r:id="rId197" xr:uid="{A10580CC-6AE9-45DA-BDF1-A6ED199E7AB7}"/>
-    <hyperlink ref="I230" r:id="rId198" xr:uid="{73AD760F-094A-49D1-8088-C0545817A477}"/>
-    <hyperlink ref="I235" r:id="rId199" xr:uid="{C234AC10-6324-4DD6-A058-75F1F9CA6F12}"/>
+    <hyperlink ref="I204" r:id="rId173" xr:uid="{42EEDCF1-F980-4D63-82CF-4DC729038221}"/>
+    <hyperlink ref="I198" r:id="rId174" xr:uid="{E099B2D0-E1B1-408A-81E6-962F50045CDA}"/>
+    <hyperlink ref="I206" r:id="rId175" xr:uid="{C5D193ED-4696-4F83-8343-8032BB681087}"/>
+    <hyperlink ref="I192" r:id="rId176" xr:uid="{28A1299C-CB07-4CBB-A8A8-007396DBE172}"/>
+    <hyperlink ref="I205" r:id="rId177" xr:uid="{A540C09D-E2A9-464E-B6EA-4D2BF932715F}"/>
+    <hyperlink ref="I195" r:id="rId178" xr:uid="{1C532CC2-B9D1-460D-8515-56F1592B3604}"/>
+    <hyperlink ref="I196" r:id="rId179" xr:uid="{F7D956AF-1FAC-4769-9788-F12DBA51D0A1}"/>
+    <hyperlink ref="I197" r:id="rId180" xr:uid="{1E5CBE72-21E0-4942-A5FB-C1798FB51093}"/>
+    <hyperlink ref="I207" r:id="rId181" xr:uid="{E01CA36B-ACE8-42AB-A793-57E82F491D41}"/>
+    <hyperlink ref="I191" r:id="rId182" xr:uid="{0544E67E-AF6D-4F5D-A38D-25CDE152AF1D}"/>
+    <hyperlink ref="I199" r:id="rId183" xr:uid="{B83136C5-9644-4ABB-BEAF-862EB577A44F}"/>
+    <hyperlink ref="I193" r:id="rId184" xr:uid="{DE4C587F-77E5-4309-A006-0343ABBAA9D0}"/>
+    <hyperlink ref="I190" r:id="rId185" xr:uid="{28DEDE56-1057-4101-ADBC-7D4B6DC6649D}"/>
+    <hyperlink ref="I194" r:id="rId186" xr:uid="{40F0F180-7743-464C-9ABD-71168C0718C7}"/>
+    <hyperlink ref="I200" r:id="rId187" xr:uid="{CCD1C6F1-C660-49C3-BFB3-1DB213616385}"/>
+    <hyperlink ref="I202" r:id="rId188" xr:uid="{9380BA53-5C1F-471D-B377-6CC3D652D2EE}"/>
+    <hyperlink ref="I203" r:id="rId189" xr:uid="{38BDDA20-AD35-4AAD-9A61-FEDB55710A94}"/>
+    <hyperlink ref="I201" r:id="rId190" xr:uid="{5C37012F-4705-474B-9B2B-BB1C567310EF}"/>
+    <hyperlink ref="I209" r:id="rId191" xr:uid="{543B344D-C918-44E6-824A-1BAC8D1A3C4A}"/>
+    <hyperlink ref="I219" r:id="rId192" xr:uid="{5649AC79-7139-4508-9C1E-0B3BD28FD5CF}"/>
+    <hyperlink ref="I218" r:id="rId193" xr:uid="{02006E33-3925-433C-80F9-427BACB29AB2}"/>
+    <hyperlink ref="I231" r:id="rId194" xr:uid="{A6387C04-B74B-4755-A998-575207C6D7B8}"/>
+    <hyperlink ref="I236" r:id="rId195" xr:uid="{7D075796-42BC-4E52-B3DC-3AED5CC2B2AF}"/>
+    <hyperlink ref="I210" r:id="rId196" xr:uid="{5BA71668-ECB7-431E-8748-3B21BB00FB80}"/>
+    <hyperlink ref="I220" r:id="rId197" xr:uid="{A10580CC-6AE9-45DA-BDF1-A6ED199E7AB7}"/>
+    <hyperlink ref="I232" r:id="rId198" xr:uid="{73AD760F-094A-49D1-8088-C0545817A477}"/>
+    <hyperlink ref="I237" r:id="rId199" xr:uid="{C234AC10-6324-4DD6-A058-75F1F9CA6F12}"/>
     <hyperlink ref="I127" r:id="rId200" xr:uid="{F5C97B0E-A756-4DE1-841D-6B1CB25F25AB}"/>
-    <hyperlink ref="I210" r:id="rId201" xr:uid="{3A611A5A-52E7-4B2D-8E8B-91A2B3A2EFE6}"/>
-    <hyperlink ref="I221" r:id="rId202" xr:uid="{9B88E7A4-7AB9-4609-902B-447AA256A22E}"/>
-    <hyperlink ref="I237" r:id="rId203" xr:uid="{16B5784E-F92A-4463-8CA6-D1A4C1500DDC}"/>
+    <hyperlink ref="I212" r:id="rId201" xr:uid="{3A611A5A-52E7-4B2D-8E8B-91A2B3A2EFE6}"/>
+    <hyperlink ref="I223" r:id="rId202" xr:uid="{9B88E7A4-7AB9-4609-902B-447AA256A22E}"/>
+    <hyperlink ref="I239" r:id="rId203" xr:uid="{16B5784E-F92A-4463-8CA6-D1A4C1500DDC}"/>
     <hyperlink ref="I126" r:id="rId204" xr:uid="{A11B1E4A-41EF-4617-8845-21061174EC6B}"/>
     <hyperlink ref="I145" r:id="rId205" xr:uid="{D872B77B-223B-4BF0-BD8C-DAAC2B0EDC99}"/>
-    <hyperlink ref="I225" r:id="rId206" xr:uid="{C93D61B2-FB23-44D0-AE82-86CFCBE87E31}"/>
-    <hyperlink ref="I209" r:id="rId207" xr:uid="{D86B3813-9911-45F9-8FE1-97CB1D382921}"/>
-    <hyperlink ref="I206" r:id="rId208" xr:uid="{83F85360-7B3C-408F-8FC3-DC7ED9BEF52A}"/>
-    <hyperlink ref="I211" r:id="rId209" xr:uid="{81A402A6-17B5-4660-A5FA-8891051AFD8A}"/>
+    <hyperlink ref="I227" r:id="rId206" xr:uid="{C93D61B2-FB23-44D0-AE82-86CFCBE87E31}"/>
+    <hyperlink ref="I211" r:id="rId207" xr:uid="{D86B3813-9911-45F9-8FE1-97CB1D382921}"/>
+    <hyperlink ref="I208" r:id="rId208" xr:uid="{83F85360-7B3C-408F-8FC3-DC7ED9BEF52A}"/>
+    <hyperlink ref="I213" r:id="rId209" xr:uid="{81A402A6-17B5-4660-A5FA-8891051AFD8A}"/>
     <hyperlink ref="I166" r:id="rId210" xr:uid="{76B6A52C-076E-4845-B26C-F7BAA6C30430}"/>
-    <hyperlink ref="I222" r:id="rId211" xr:uid="{9A1A11F7-AD8B-47F0-87A3-8CACA6F2F4C7}"/>
-    <hyperlink ref="I226" r:id="rId212" xr:uid="{064F1840-F71C-47C2-9F8A-E9CC6E203674}"/>
-    <hyperlink ref="I224" r:id="rId213" xr:uid="{265E5CC6-C099-4295-AF9E-712181DBF85D}"/>
-    <hyperlink ref="I236" r:id="rId214" xr:uid="{BF82DE43-9D68-46B0-B3F9-260F9A6DB8A8}"/>
-    <hyperlink ref="I213" r:id="rId215" xr:uid="{12901D47-8902-41FB-BE93-FB91AA7CE8E5}"/>
-    <hyperlink ref="I232" r:id="rId216" xr:uid="{C139B65F-A76A-492E-A650-5F3ACF0EA096}"/>
-    <hyperlink ref="I219" r:id="rId217" xr:uid="{5BFBC30B-5F84-47F5-87A8-924092803241}"/>
+    <hyperlink ref="I224" r:id="rId211" xr:uid="{9A1A11F7-AD8B-47F0-87A3-8CACA6F2F4C7}"/>
+    <hyperlink ref="I228" r:id="rId212" xr:uid="{064F1840-F71C-47C2-9F8A-E9CC6E203674}"/>
+    <hyperlink ref="I226" r:id="rId213" xr:uid="{265E5CC6-C099-4295-AF9E-712181DBF85D}"/>
+    <hyperlink ref="I238" r:id="rId214" xr:uid="{BF82DE43-9D68-46B0-B3F9-260F9A6DB8A8}"/>
+    <hyperlink ref="I215" r:id="rId215" xr:uid="{12901D47-8902-41FB-BE93-FB91AA7CE8E5}"/>
+    <hyperlink ref="I234" r:id="rId216" xr:uid="{C139B65F-A76A-492E-A650-5F3ACF0EA096}"/>
+    <hyperlink ref="I221" r:id="rId217" xr:uid="{5BFBC30B-5F84-47F5-87A8-924092803241}"/>
     <hyperlink ref="I131" r:id="rId218" xr:uid="{C2FEEE03-74B0-4453-9355-675F9D619B6D}"/>
-    <hyperlink ref="I214" r:id="rId219" xr:uid="{D9A906FF-B66D-412D-8BE7-45B3B2CF68CB}"/>
-    <hyperlink ref="I223" r:id="rId220" xr:uid="{52768E1D-0D83-4158-9941-D3FE248FCC03}"/>
-    <hyperlink ref="I231" r:id="rId221" xr:uid="{90E84A57-1F82-4F32-9D1C-7865BC6BE4A4}"/>
-    <hyperlink ref="I227" r:id="rId222" xr:uid="{671CCE4D-4E93-4F47-92EF-D7CD6C4947E4}"/>
-    <hyperlink ref="I238" r:id="rId223" xr:uid="{4E694A67-55C4-480D-BB42-451F3B91FD3D}"/>
-    <hyperlink ref="I239" r:id="rId224" xr:uid="{D1A65E2F-5174-4124-8DA4-11E5CE27BA0E}"/>
-    <hyperlink ref="I215" r:id="rId225" xr:uid="{342E0CE5-B06A-44F1-B1E3-0F01DA98C0F8}"/>
-    <hyperlink ref="I233" r:id="rId226" xr:uid="{9A2773ED-FCEC-4754-9FD4-F817C8BEE422}"/>
-    <hyperlink ref="I228" r:id="rId227" xr:uid="{AC3FDBEE-621F-49CA-8B77-8C0142C94062}"/>
+    <hyperlink ref="I216" r:id="rId219" xr:uid="{D9A906FF-B66D-412D-8BE7-45B3B2CF68CB}"/>
+    <hyperlink ref="I225" r:id="rId220" xr:uid="{52768E1D-0D83-4158-9941-D3FE248FCC03}"/>
+    <hyperlink ref="I233" r:id="rId221" xr:uid="{90E84A57-1F82-4F32-9D1C-7865BC6BE4A4}"/>
+    <hyperlink ref="I229" r:id="rId222" xr:uid="{671CCE4D-4E93-4F47-92EF-D7CD6C4947E4}"/>
+    <hyperlink ref="I240" r:id="rId223" xr:uid="{4E694A67-55C4-480D-BB42-451F3B91FD3D}"/>
+    <hyperlink ref="I241" r:id="rId224" xr:uid="{D1A65E2F-5174-4124-8DA4-11E5CE27BA0E}"/>
+    <hyperlink ref="I217" r:id="rId225" xr:uid="{342E0CE5-B06A-44F1-B1E3-0F01DA98C0F8}"/>
+    <hyperlink ref="I235" r:id="rId226" xr:uid="{9A2773ED-FCEC-4754-9FD4-F817C8BEE422}"/>
+    <hyperlink ref="I230" r:id="rId227" xr:uid="{AC3FDBEE-621F-49CA-8B77-8C0142C94062}"/>
     <hyperlink ref="I178" r:id="rId228" xr:uid="{2B381187-46B1-4F12-B990-A74CDA4E63E3}"/>
     <hyperlink ref="I179" r:id="rId229" xr:uid="{79FF6202-A7D6-4257-94F7-CC7570579AC9}"/>
     <hyperlink ref="I177" r:id="rId230" xr:uid="{D6BF7B75-1E2D-4B1B-823D-B86EBC85730E}"/>
